--- a/data/uac_audio_config.xlsx
+++ b/data/uac_audio_config.xlsx
@@ -1,24 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/SystemDocumentation/github/uactechdoc/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0BDC8A1-10B0-8A40-B4B9-DE4298664F41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CA2FB2B-07DA-6B44-A9CB-9A3B63E47946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="140" yWindow="920" windowWidth="14880" windowHeight="18580" activeTab="1" xr2:uid="{C6DAFA3B-D3DD-0B4C-98F6-8BDAEB6918C5}"/>
+    <workbookView xWindow="6540" yWindow="920" windowWidth="23700" windowHeight="18580" activeTab="4" xr2:uid="{C6DAFA3B-D3DD-0B4C-98F6-8BDAEB6918C5}"/>
   </bookViews>
   <sheets>
     <sheet name="ConsoleInputs" sheetId="1" r:id="rId1"/>
-    <sheet name="dLive Inputs" sheetId="6" r:id="rId2"/>
-    <sheet name="ConsoleOutputs" sheetId="4" r:id="rId3"/>
+    <sheet name="Sources" sheetId="6" r:id="rId2"/>
+    <sheet name="Outputs" sheetId="4" r:id="rId3"/>
     <sheet name="DanteDevices" sheetId="2" r:id="rId4"/>
     <sheet name="DantePatch" sheetId="3" r:id="rId5"/>
-    <sheet name="dante_outputs" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1457" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="277">
   <si>
     <t>Channel</t>
   </si>
@@ -436,234 +435,39 @@
     <t>Omni Lav</t>
   </si>
   <si>
-    <t>Omni 1</t>
-  </si>
-  <si>
-    <t>Output</t>
-  </si>
-  <si>
     <t>Mon 1</t>
   </si>
   <si>
-    <t>Front Line Vox 1 monitor</t>
-  </si>
-  <si>
     <t>Mon 2</t>
   </si>
   <si>
-    <t>Front Line Vox 2 monitor</t>
-  </si>
-  <si>
-    <t>Omni 2</t>
-  </si>
-  <si>
-    <t>Omni 3</t>
-  </si>
-  <si>
     <t>Mon 3</t>
   </si>
   <si>
-    <t>Spare</t>
-  </si>
-  <si>
-    <t>Omni 4</t>
-  </si>
-  <si>
     <t>Mon 4</t>
   </si>
   <si>
-    <t>Backline</t>
-  </si>
-  <si>
-    <t>Omni 5</t>
-  </si>
-  <si>
     <t>Mon 5</t>
   </si>
   <si>
-    <t>Drums</t>
-  </si>
-  <si>
-    <t>Omni 6</t>
-  </si>
-  <si>
     <t>Mon 6</t>
   </si>
   <si>
-    <t>Piano and Keys</t>
-  </si>
-  <si>
-    <t>Omni 7</t>
-  </si>
-  <si>
-    <t>Omni 8</t>
-  </si>
-  <si>
-    <t>Omni 9</t>
-  </si>
-  <si>
-    <t>Omni 10</t>
-  </si>
-  <si>
-    <t>Omni 11</t>
-  </si>
-  <si>
-    <t>Omni 12</t>
-  </si>
-  <si>
-    <t>Omni 13</t>
-  </si>
-  <si>
-    <t>Omni 14</t>
-  </si>
-  <si>
-    <t>Omni 15</t>
-  </si>
-  <si>
-    <t>Omni 16</t>
-  </si>
-  <si>
     <t>Record</t>
   </si>
   <si>
-    <t>Slot</t>
-  </si>
-  <si>
-    <t>ch 33 Insert Out</t>
-  </si>
-  <si>
-    <t>ch 34 Insert Out</t>
-  </si>
-  <si>
-    <t>ch 35 Insert Out</t>
-  </si>
-  <si>
-    <t>ch 36 Insert Out</t>
-  </si>
-  <si>
-    <t>ch 37 Insert Out</t>
-  </si>
-  <si>
-    <t>ch 38 Insert Out</t>
-  </si>
-  <si>
-    <t>ch 39 Insert Out</t>
-  </si>
-  <si>
-    <t>ch 40 Insert Out</t>
-  </si>
-  <si>
-    <t>ch 47 Insert Out</t>
-  </si>
-  <si>
-    <t>ch 48 Insert Out</t>
-  </si>
-  <si>
     <t>Room Mic</t>
   </si>
   <si>
-    <t>Source</t>
-  </si>
-  <si>
-    <t>Direct Out</t>
-  </si>
-  <si>
-    <t>Mx 11</t>
-  </si>
-  <si>
-    <t>Mx 12</t>
-  </si>
-  <si>
-    <t>Mx 15</t>
-  </si>
-  <si>
-    <t>Mx 13</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Mx 14</t>
-  </si>
-  <si>
-    <t>ST L</t>
-  </si>
-  <si>
     <t>Kick</t>
   </si>
   <si>
     <t>Snare</t>
   </si>
   <si>
-    <t>3,4,5,6</t>
-  </si>
-  <si>
-    <t>7,8,9</t>
-  </si>
-  <si>
-    <t>19, 20</t>
-  </si>
-  <si>
-    <t>46,47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toms </t>
-  </si>
-  <si>
-    <t>Cymbals &amp; HiHat</t>
-  </si>
-  <si>
-    <t>B3 Lo &amp; Hi</t>
-  </si>
-  <si>
-    <t>Room Mics</t>
-  </si>
-  <si>
-    <t>Get out of trouble</t>
-  </si>
-  <si>
-    <t>Card</t>
-  </si>
-  <si>
-    <t>Slot 2</t>
-  </si>
-  <si>
-    <t>Card Channel</t>
-  </si>
-  <si>
-    <t>Related Inputs</t>
-  </si>
-  <si>
-    <t>Piano Lo</t>
-  </si>
-  <si>
-    <t>Piano Hi</t>
-  </si>
-  <si>
-    <t>Synth</t>
-  </si>
-  <si>
     <t>Bass</t>
   </si>
   <si>
-    <t>Electric Guitar</t>
-  </si>
-  <si>
-    <t>Acoustic Guitar</t>
-  </si>
-  <si>
-    <t>Recording - Get out of trouble</t>
-  </si>
-  <si>
-    <t>Plate Reverb</t>
-  </si>
-  <si>
-    <t>Hall Reverb</t>
-  </si>
-  <si>
-    <t>Delay</t>
-  </si>
-  <si>
     <t>ZAIU-B003</t>
   </si>
   <si>
@@ -685,21 +489,6 @@
     <t>Ken</t>
   </si>
   <si>
-    <t>OutputType</t>
-  </si>
-  <si>
-    <t>analog</t>
-  </si>
-  <si>
-    <t>dante</t>
-  </si>
-  <si>
-    <t>Drum mix</t>
-  </si>
-  <si>
-    <t>Bass mix</t>
-  </si>
-  <si>
     <t>Room Mic mix</t>
   </si>
   <si>
@@ -877,12 +666,6 @@
     <t>MixRack</t>
   </si>
   <si>
-    <t>Djembe</t>
-  </si>
-  <si>
-    <t>Perc</t>
-  </si>
-  <si>
     <t>Eg1</t>
   </si>
   <si>
@@ -895,12 +678,6 @@
     <t>Ag2</t>
   </si>
   <si>
-    <t>Violin</t>
-  </si>
-  <si>
-    <t>Flute</t>
-  </si>
-  <si>
     <t>Sz L</t>
   </si>
   <si>
@@ -1006,18 +783,9 @@
     <t>Talkback</t>
   </si>
   <si>
-    <t>IO1 (Dante)</t>
-  </si>
-  <si>
-    <t>DX1 (DX168)</t>
-  </si>
-  <si>
     <t>S5000</t>
   </si>
   <si>
-    <t>?</t>
-  </si>
-  <si>
     <t>na</t>
   </si>
   <si>
@@ -1037,13 +805,79 @@
   </si>
   <si>
     <t>dLive Input (VSC)</t>
+  </si>
+  <si>
+    <t>Inst10</t>
+  </si>
+  <si>
+    <t>Inst11</t>
+  </si>
+  <si>
+    <t>Inst12</t>
+  </si>
+  <si>
+    <t>Inst13</t>
+  </si>
+  <si>
+    <t>Inst14</t>
+  </si>
+  <si>
+    <t>DX1-DX168</t>
+  </si>
+  <si>
+    <t>IO1-Dante</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t>Mon 7</t>
+  </si>
+  <si>
+    <t>Mon 8</t>
+  </si>
+  <si>
+    <t>Main Left</t>
+  </si>
+  <si>
+    <t>Main Right</t>
+  </si>
+  <si>
+    <t>HH11/BP04</t>
+  </si>
+  <si>
+    <t>HH12/BP05</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1065,19 +899,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -1085,7 +906,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1098,14 +919,8 @@
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="-0.24994659260841701"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1146,103 +961,62 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="12">
     <dxf>
       <font>
         <b val="0"/>
@@ -1259,24 +1033,6 @@
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
       </font>
     </dxf>
     <dxf>
@@ -1314,27 +1070,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color rgb="FF333333"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1412,7 +1148,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2311C7CC-3CAB-D248-BDEA-A3EE7A3D8D2D}" name="Table1" displayName="Table1" ref="A1:G69" totalsRowShown="0">
   <autoFilter ref="A1:G69" xr:uid="{2311C7CC-3CAB-D248-BDEA-A3EE7A3D8D2D}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{DBB20B09-FB33-6247-AD08-E97214AF1637}" name="Device" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{DBB20B09-FB33-6247-AD08-E97214AF1637}" name="Device" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{88D57E0E-91FD-7D4F-89A1-2264885642B2}" name="Channel"/>
     <tableColumn id="3" xr3:uid="{9E11E5CF-4755-1943-8DAE-DE6526F4BA0B}" name="Usage"/>
     <tableColumn id="4" xr3:uid="{583EBD09-A311-8549-AD99-0519A1BA7038}" name="Type"/>
@@ -1425,36 +1161,32 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{ABDCAFCE-FDD5-DB4C-822F-E432F9DD29BB}" name="Table5" displayName="Table5" ref="A1:H129" totalsRowShown="0" headerRowDxfId="17">
-  <autoFilter ref="A1:H129" xr:uid="{ABDCAFCE-FDD5-DB4C-822F-E432F9DD29BB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{ABDCAFCE-FDD5-DB4C-822F-E432F9DD29BB}" name="Table5" displayName="Table5" ref="A1:H193" totalsRowShown="0" headerRowDxfId="10">
+  <autoFilter ref="A1:H193" xr:uid="{ABDCAFCE-FDD5-DB4C-822F-E432F9DD29BB}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{0E6A60A7-3B9E-1245-B6B0-8749886FC86A}" name="dLive Inputs (normal)" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{0E6A60A7-3B9E-1245-B6B0-8749886FC86A}" name="dLive Inputs (normal)" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{826E7323-F691-5442-912B-E0CBAAA4428D}" name="Name"/>
     <tableColumn id="3" xr3:uid="{00D3393C-0BBC-DD4C-ADA5-7B6C44F683D1}" name="Device"/>
-    <tableColumn id="4" xr3:uid="{4DD0492B-5A42-3648-8203-7D62B858D626}" name="Port" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{B2A1F6AB-34D2-3C40-9341-45876A1E69E4}" name="G002 Output (VSC)" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{5538FAC4-E095-A840-8D18-DEB7B0714DD4}" name="dLive Input (VSC)" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{B0DA74F1-771E-5C46-BCFC-E9FEA4B38663}" name="E001 input (Reaper)" dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{14F24F0E-BD9E-0B40-807A-02AF9FEEC7E2}" name="Konductor Input" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{4DD0492B-5A42-3648-8203-7D62B858D626}" name="Port" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{B2A1F6AB-34D2-3C40-9341-45876A1E69E4}" name="G002 Output (VSC)" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{5538FAC4-E095-A840-8D18-DEB7B0714DD4}" name="dLive Input (VSC)" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{B0DA74F1-771E-5C46-BCFC-E9FEA4B38663}" name="E001 input (Reaper)" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{14F24F0E-BD9E-0B40-807A-02AF9FEEC7E2}" name="Konductor Input" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1765E8B9-222B-B446-9BF3-DEB443021D72}" name="Table2" displayName="Table2" ref="A1:H33" totalsRowShown="0">
-  <autoFilter ref="A1:H33" xr:uid="{1765E8B9-222B-B446-9BF3-DEB443021D72}"/>
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{9EDC3475-3A92-D44A-975D-D24A46894B36}" name="Device" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{0BC25048-D076-B747-A580-B06384E0734E}" name="OutputType" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{83A4B198-2B6D-7B4A-902F-927F8B9185BE}" name="Output" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{BAE3D02E-A444-D548-A15E-B6D66C01F6ED}" name="Label"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1765E8B9-222B-B446-9BF3-DEB443021D72}" name="Table2" displayName="Table2" ref="A1:D15" totalsRowShown="0">
+  <autoFilter ref="A1:D15" xr:uid="{1765E8B9-222B-B446-9BF3-DEB443021D72}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{9EDC3475-3A92-D44A-975D-D24A46894B36}" name="Device" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{F6B5B5E9-83BF-B642-9AF8-17BE16B9D119}" name="Port" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{BAE3D02E-A444-D548-A15E-B6D66C01F6ED}" name="Name"/>
     <tableColumn id="5" xr3:uid="{D96C6764-0724-E443-8AE6-A2E45C90F9DF}" name="Usage">
-      <calculatedColumnFormula>D2</calculatedColumnFormula>
+      <calculatedColumnFormula>C2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{153EC7B0-5CB8-E94E-82DA-2B29BE73E8EC}" name="Slot"/>
-    <tableColumn id="7" xr3:uid="{93ADA22B-EB5C-D545-9D5C-27754407FE07}" name="NetworkDeviceOut"/>
-    <tableColumn id="8" xr3:uid="{E9C29EFE-258E-4B46-B379-7AF4A5A12C07}" name="NetworkDeviceChannelOut"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1464,28 +1196,13 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{83E74022-6F6B-1045-B8C5-B98B3D21E9BD}" name="Table4" displayName="Table4" ref="A1:G145" totalsRowShown="0">
   <autoFilter ref="A1:G145" xr:uid="{83E74022-6F6B-1045-B8C5-B98B3D21E9BD}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{E602AD31-C3D3-FD43-8372-B5858DBF28D9}" name="Device" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{B02630D7-D7C3-E441-9182-A59F371F65DE}" name="NetworkDevice" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{E602AD31-C3D3-FD43-8372-B5858DBF28D9}" name="Device" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{B02630D7-D7C3-E441-9182-A59F371F65DE}" name="NetworkDevice" dataDxfId="0"/>
     <tableColumn id="3" xr3:uid="{2E2A113B-B3DA-6B4E-91A4-24182F327EB9}" name="NetworkDeviceChannel"/>
     <tableColumn id="4" xr3:uid="{3DC344F6-23E3-D54C-9E87-5780E47CCA37}" name="InOut"/>
     <tableColumn id="7" xr3:uid="{D2023134-14D1-204E-8572-D20AE5BB355A}" name="Used"/>
     <tableColumn id="5" xr3:uid="{E3E37727-A5BA-2646-B1EA-018378FA4754}" name="Label"/>
     <tableColumn id="6" xr3:uid="{7779A5DE-B803-EB45-81AA-580D295F0233}" name="Usage"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4F1912FF-9B7B-DD40-A31B-6AFC18D6A66C}" name="Table3" displayName="Table3" ref="A1:F17" totalsRowShown="0" headerRowDxfId="5">
-  <autoFilter ref="A1:F17" xr:uid="{4F1912FF-9B7B-DD40-A31B-6AFC18D6A66C}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{4E358B1B-8ADB-D74E-A54A-769E22787376}" name="Device" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{B6EC83A2-1A27-5146-9741-FBC9BBA84F41}" name="Card"/>
-    <tableColumn id="3" xr3:uid="{52135101-6543-8D46-A88B-254E00FCBC19}" name="Card Channel" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{138F406F-59C6-264F-90AE-F2674B19C317}" name="Source" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{FB840414-1864-B946-BDC0-DA99FA659BDD}" name="Related Inputs" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{DEA866AD-3B1E-3E46-A00A-B618F26B8C2E}" name="Usage" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2599,7 +2316,7 @@
         <v>43</v>
       </c>
       <c r="C44" t="s">
-        <v>210</v>
+        <v>145</v>
       </c>
       <c r="D44" t="s">
         <v>21</v>
@@ -2608,7 +2325,7 @@
         <v>122</v>
       </c>
       <c r="F44" t="s">
-        <v>207</v>
+        <v>142</v>
       </c>
       <c r="G44">
         <v>2</v>
@@ -2622,7 +2339,7 @@
         <v>44</v>
       </c>
       <c r="C45" t="s">
-        <v>211</v>
+        <v>146</v>
       </c>
       <c r="D45" t="s">
         <v>21</v>
@@ -2631,7 +2348,7 @@
         <v>122</v>
       </c>
       <c r="F45" t="s">
-        <v>207</v>
+        <v>142</v>
       </c>
       <c r="G45">
         <v>3</v>
@@ -2645,16 +2362,16 @@
         <v>45</v>
       </c>
       <c r="C46" t="s">
-        <v>212</v>
+        <v>147</v>
       </c>
       <c r="D46" t="s">
-        <v>213</v>
+        <v>148</v>
       </c>
       <c r="E46" t="s">
         <v>122</v>
       </c>
       <c r="F46" t="s">
-        <v>207</v>
+        <v>142</v>
       </c>
       <c r="G46">
         <v>4</v>
@@ -2674,7 +2391,7 @@
         <v>16</v>
       </c>
       <c r="E47" t="s">
-        <v>172</v>
+        <v>138</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
@@ -2691,7 +2408,7 @@
         <v>16</v>
       </c>
       <c r="E48" t="s">
-        <v>172</v>
+        <v>138</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
@@ -2708,7 +2425,7 @@
         <v>16</v>
       </c>
       <c r="E49" t="s">
-        <v>172</v>
+        <v>138</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
@@ -2839,7 +2556,7 @@
         <v>122</v>
       </c>
       <c r="F56" t="s">
-        <v>207</v>
+        <v>142</v>
       </c>
       <c r="G56">
         <v>1</v>
@@ -2862,7 +2579,7 @@
         <v>122</v>
       </c>
       <c r="F57" t="s">
-        <v>207</v>
+        <v>142</v>
       </c>
       <c r="G57">
         <v>2</v>
@@ -2885,7 +2602,7 @@
         <v>122</v>
       </c>
       <c r="F58" t="s">
-        <v>207</v>
+        <v>142</v>
       </c>
       <c r="G58">
         <v>3</v>
@@ -2908,7 +2625,7 @@
         <v>122</v>
       </c>
       <c r="F59" t="s">
-        <v>207</v>
+        <v>142</v>
       </c>
       <c r="G59">
         <v>4</v>
@@ -3094,1846 +2811,2427 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC9B722B-A685-AA47-B15D-4CB871BDA8B9}">
-  <dimension ref="A1:H129"/>
+  <dimension ref="A1:H193"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" style="6" customWidth="1"/>
+    <col min="1" max="1" width="12.83203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="14.6640625" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" style="6"/>
-    <col min="5" max="5" width="9.83203125" style="6" customWidth="1"/>
-    <col min="6" max="8" width="10.83203125" style="6"/>
+    <col min="4" max="4" width="10.83203125" style="2"/>
+    <col min="5" max="5" width="9.83203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="25" style="2" customWidth="1"/>
+    <col min="7" max="8" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="51" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
-        <v>328</v>
+      <c r="A1" s="7" t="s">
+        <v>251</v>
       </c>
       <c r="B1" t="s">
-        <v>274</v>
+        <v>204</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="E1" s="14" t="s">
-        <v>327</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>331</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>330</v>
-      </c>
-      <c r="H1" s="14" t="s">
-        <v>329</v>
+      <c r="D1" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="6">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>276</v>
+        <v>206</v>
       </c>
       <c r="C2" t="s">
-        <v>277</v>
-      </c>
-      <c r="D2" s="6">
+        <v>207</v>
+      </c>
+      <c r="D2" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="6">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
+      <c r="B3" t="s">
+        <v>206</v>
+      </c>
       <c r="C3" t="s">
-        <v>277</v>
-      </c>
-      <c r="D3" s="6">
+        <v>207</v>
+      </c>
+      <c r="D3" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="6">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>277</v>
-      </c>
-      <c r="D4" s="6">
+        <v>207</v>
+      </c>
+      <c r="D4" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="6">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>277</v>
-      </c>
-      <c r="D5" s="6">
+        <v>207</v>
+      </c>
+      <c r="D5" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="6">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>277</v>
-      </c>
-      <c r="D6" s="6">
+        <v>207</v>
+      </c>
+      <c r="D6" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="6">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>277</v>
-      </c>
-      <c r="D7" s="6">
+        <v>207</v>
+      </c>
+      <c r="D7" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="6">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>277</v>
-      </c>
-      <c r="D8" s="6">
+        <v>207</v>
+      </c>
+      <c r="D8" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="6">
+      <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>277</v>
-      </c>
-      <c r="D9" s="6">
+        <v>207</v>
+      </c>
+      <c r="D9" s="2">
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="6">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>277</v>
-      </c>
-      <c r="D10" s="6">
+        <v>207</v>
+      </c>
+      <c r="D10" s="2">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="6">
+      <c r="A11" s="2">
         <v>10</v>
       </c>
+      <c r="B11" t="s">
+        <v>255</v>
+      </c>
       <c r="C11" t="s">
-        <v>277</v>
-      </c>
-      <c r="D11" s="6">
+        <v>207</v>
+      </c>
+      <c r="D11" s="2">
         <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="6">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
+      <c r="B12" t="s">
+        <v>256</v>
+      </c>
       <c r="C12" t="s">
-        <v>277</v>
-      </c>
-      <c r="D12" s="6">
+        <v>207</v>
+      </c>
+      <c r="D12" s="2">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="6">
+      <c r="A13" s="2">
         <v>12</v>
       </c>
+      <c r="B13" t="s">
+        <v>257</v>
+      </c>
       <c r="C13" t="s">
-        <v>277</v>
-      </c>
-      <c r="D13" s="6">
+        <v>207</v>
+      </c>
+      <c r="D13" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="6">
+      <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>278</v>
+        <v>258</v>
       </c>
       <c r="C14" t="s">
-        <v>277</v>
-      </c>
-      <c r="D14" s="6">
+        <v>207</v>
+      </c>
+      <c r="D14" s="2">
         <v>13</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="2">
         <v>14</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="2">
         <f>Table5[[#This Row],[G002 Output (VSC)]]+64</f>
         <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="6">
+      <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="C15" t="s">
-        <v>277</v>
-      </c>
-      <c r="D15" s="6">
+        <v>207</v>
+      </c>
+      <c r="D15" s="2">
         <v>14</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="2">
         <v>15</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="2">
         <f>Table5[[#This Row],[G002 Output (VSC)]]+64</f>
         <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="6">
+      <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>277</v>
-      </c>
-      <c r="D16" s="6">
+        <v>207</v>
+      </c>
+      <c r="D16" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="6">
+      <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>277</v>
-      </c>
-      <c r="D17" s="6">
+        <v>207</v>
+      </c>
+      <c r="D17" s="2">
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" s="6">
+      <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>277</v>
-      </c>
-      <c r="D18" s="6">
+        <v>207</v>
+      </c>
+      <c r="D18" s="2">
         <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" s="6">
+      <c r="A19" s="2">
         <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>277</v>
-      </c>
-      <c r="D19" s="6">
+        <v>207</v>
+      </c>
+      <c r="D19" s="2">
         <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" s="6">
+      <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>280</v>
+        <v>208</v>
       </c>
       <c r="C20" t="s">
-        <v>277</v>
-      </c>
-      <c r="D20" s="6">
+        <v>207</v>
+      </c>
+      <c r="D20" s="2">
         <v>19</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="2">
         <v>16</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="2">
         <f>Table5[[#This Row],[G002 Output (VSC)]]+64</f>
         <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" s="6">
+      <c r="A21" s="2">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>281</v>
+        <v>209</v>
       </c>
       <c r="C21" t="s">
-        <v>277</v>
-      </c>
-      <c r="D21" s="6">
+        <v>207</v>
+      </c>
+      <c r="D21" s="2">
         <v>20</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="2">
         <v>17</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F21" s="2">
         <f>Table5[[#This Row],[G002 Output (VSC)]]+64</f>
         <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" s="6">
+      <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>282</v>
+        <v>210</v>
       </c>
       <c r="C22" t="s">
-        <v>277</v>
-      </c>
-      <c r="D22" s="6">
+        <v>207</v>
+      </c>
+      <c r="D22" s="2">
         <v>21</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="2">
         <v>18</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F22" s="2">
         <f>Table5[[#This Row],[G002 Output (VSC)]]+64</f>
         <v>82</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" s="6">
+      <c r="A23" s="2">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>283</v>
+        <v>211</v>
       </c>
       <c r="C23" t="s">
-        <v>277</v>
-      </c>
-      <c r="D23" s="6">
+        <v>207</v>
+      </c>
+      <c r="D23" s="2">
         <v>22</v>
       </c>
-      <c r="E23" s="6">
+      <c r="E23" s="2">
         <v>19</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="2">
         <f>Table5[[#This Row],[G002 Output (VSC)]]+64</f>
         <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" s="6">
+      <c r="A24" s="2">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
-        <v>284</v>
-      </c>
       <c r="C24" t="s">
-        <v>277</v>
-      </c>
-      <c r="D24" s="6">
+        <v>207</v>
+      </c>
+      <c r="D24" s="2">
         <v>23</v>
       </c>
-      <c r="E24" s="6">
-        <v>20</v>
-      </c>
-      <c r="F24" s="6">
+      <c r="E24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="2" t="e">
         <f>Table5[[#This Row],[G002 Output (VSC)]]+64</f>
-        <v>84</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" s="6">
+      <c r="A25" s="2">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
-        <v>285</v>
-      </c>
       <c r="C25" t="s">
-        <v>277</v>
-      </c>
-      <c r="D25" s="6">
+        <v>207</v>
+      </c>
+      <c r="D25" s="2">
         <v>24</v>
       </c>
-      <c r="E25" s="6">
-        <v>21</v>
-      </c>
-      <c r="F25" s="6">
-        <f>Table5[[#This Row],[G002 Output (VSC)]]+64</f>
-        <v>85</v>
-      </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A26" s="6">
+      <c r="A26" s="2">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>246</v>
+        <v>176</v>
       </c>
       <c r="C26" t="s">
-        <v>277</v>
-      </c>
-      <c r="D26" s="6">
+        <v>207</v>
+      </c>
+      <c r="D26" s="2">
         <v>25</v>
       </c>
-      <c r="E26" s="6">
+      <c r="E26" s="2">
         <v>22</v>
       </c>
-      <c r="F26" s="6">
+      <c r="F26" s="2">
         <f>Table5[[#This Row],[G002 Output (VSC)]]+64</f>
         <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A27" s="6">
+      <c r="A27" s="2">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>248</v>
+        <v>178</v>
       </c>
       <c r="C27" t="s">
-        <v>277</v>
-      </c>
-      <c r="D27" s="6">
+        <v>207</v>
+      </c>
+      <c r="D27" s="2">
         <v>26</v>
       </c>
-      <c r="E27" s="6">
+      <c r="E27" s="2">
         <v>23</v>
       </c>
-      <c r="F27" s="6">
+      <c r="F27" s="2">
         <f>Table5[[#This Row],[G002 Output (VSC)]]+64</f>
         <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A28" s="6">
+      <c r="A28" s="2">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>286</v>
+        <v>212</v>
       </c>
       <c r="C28" t="s">
-        <v>277</v>
-      </c>
-      <c r="D28" s="6">
+        <v>207</v>
+      </c>
+      <c r="D28" s="2">
         <v>27</v>
       </c>
-      <c r="E28" s="6">
+      <c r="E28" s="2">
         <v>24</v>
       </c>
-      <c r="F28" s="6">
+      <c r="F28" s="2">
         <f>Table5[[#This Row],[G002 Output (VSC)]]+64</f>
         <v>88</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A29" s="6">
+      <c r="A29" s="2">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>287</v>
+        <v>213</v>
       </c>
       <c r="C29" t="s">
-        <v>277</v>
-      </c>
-      <c r="D29" s="6">
+        <v>207</v>
+      </c>
+      <c r="D29" s="2">
         <v>28</v>
       </c>
-      <c r="E29" s="6">
+      <c r="E29" s="2">
         <v>25</v>
       </c>
-      <c r="F29" s="6">
+      <c r="F29" s="2">
         <f>Table5[[#This Row],[G002 Output (VSC)]]+64</f>
         <v>89</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" s="6">
+      <c r="A30" s="2">
         <v>29</v>
       </c>
       <c r="C30" t="s">
-        <v>277</v>
-      </c>
-      <c r="D30" s="6">
+        <v>207</v>
+      </c>
+      <c r="D30" s="2">
         <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A31" s="6">
+      <c r="A31" s="2">
         <v>30</v>
       </c>
       <c r="C31" t="s">
-        <v>277</v>
-      </c>
-      <c r="D31" s="6">
+        <v>207</v>
+      </c>
+      <c r="D31" s="2">
         <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A32" s="6">
+      <c r="A32" s="2">
         <v>31</v>
       </c>
       <c r="C32" t="s">
-        <v>277</v>
-      </c>
-      <c r="D32" s="6">
+        <v>207</v>
+      </c>
+      <c r="D32" s="2">
         <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A33" s="6">
+      <c r="A33" s="2">
         <v>32</v>
       </c>
       <c r="C33" t="s">
-        <v>277</v>
-      </c>
-      <c r="D33" s="6">
+        <v>207</v>
+      </c>
+      <c r="D33" s="2">
         <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A34" s="6">
+      <c r="A34" s="2">
         <v>33</v>
       </c>
       <c r="C34" t="s">
-        <v>277</v>
-      </c>
-      <c r="D34" s="6">
+        <v>207</v>
+      </c>
+      <c r="D34" s="2">
         <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A35" s="6">
+      <c r="A35" s="2">
         <v>34</v>
       </c>
       <c r="C35" t="s">
-        <v>277</v>
-      </c>
-      <c r="D35" s="6">
+        <v>207</v>
+      </c>
+      <c r="D35" s="2">
         <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A36" s="6">
+      <c r="A36" s="2">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>288</v>
+        <v>214</v>
       </c>
       <c r="C36" t="s">
-        <v>277</v>
-      </c>
-      <c r="D36" s="6">
+        <v>207</v>
+      </c>
+      <c r="D36" s="2">
         <v>35</v>
       </c>
-      <c r="E36" s="6">
+      <c r="E36" s="2">
         <v>26</v>
       </c>
-      <c r="F36" s="6">
+      <c r="F36" s="2">
         <f>Table5[[#This Row],[G002 Output (VSC)]]+64</f>
         <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A37" s="6">
+      <c r="A37" s="2">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>289</v>
+        <v>215</v>
       </c>
       <c r="C37" t="s">
-        <v>277</v>
-      </c>
-      <c r="D37" s="6">
+        <v>207</v>
+      </c>
+      <c r="D37" s="2">
         <v>36</v>
       </c>
-      <c r="E37" s="6">
+      <c r="E37" s="2">
         <v>27</v>
       </c>
-      <c r="F37" s="6">
+      <c r="F37" s="2">
         <f>Table5[[#This Row],[G002 Output (VSC)]]+64</f>
         <v>91</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A38" s="6">
+      <c r="A38" s="2">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>290</v>
+        <v>216</v>
       </c>
       <c r="C38" t="s">
-        <v>277</v>
-      </c>
-      <c r="D38" s="6">
+        <v>207</v>
+      </c>
+      <c r="D38" s="2">
         <v>37</v>
       </c>
-      <c r="E38" s="6">
+      <c r="E38" s="2">
         <v>28</v>
       </c>
-      <c r="F38" s="6">
+      <c r="F38" s="2">
         <f>Table5[[#This Row],[G002 Output (VSC)]]+64</f>
         <v>92</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A39" s="6">
+      <c r="A39" s="2">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>291</v>
+        <v>217</v>
       </c>
       <c r="C39" t="s">
-        <v>277</v>
-      </c>
-      <c r="D39" s="6">
+        <v>207</v>
+      </c>
+      <c r="D39" s="2">
         <v>38</v>
       </c>
-      <c r="E39" s="6">
+      <c r="E39" s="2">
         <v>29</v>
       </c>
-      <c r="F39" s="6">
+      <c r="F39" s="2">
         <f>Table5[[#This Row],[G002 Output (VSC)]]+64</f>
         <v>93</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A40" s="6">
+      <c r="A40" s="2">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>292</v>
+        <v>218</v>
       </c>
       <c r="C40" t="s">
-        <v>277</v>
-      </c>
-      <c r="D40" s="6">
+        <v>207</v>
+      </c>
+      <c r="D40" s="2">
         <v>39</v>
       </c>
-      <c r="E40" s="6" t="s">
-        <v>325</v>
+      <c r="E40" s="2" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A41" s="6">
+      <c r="A41" s="2">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>293</v>
+        <v>219</v>
       </c>
       <c r="C41" t="s">
-        <v>277</v>
-      </c>
-      <c r="D41" s="6">
+        <v>207</v>
+      </c>
+      <c r="D41" s="2">
         <v>40</v>
       </c>
-      <c r="E41" s="6" t="s">
-        <v>325</v>
+      <c r="E41" s="2" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A42" s="6">
+      <c r="A42" s="2">
         <v>41</v>
       </c>
       <c r="C42" t="s">
-        <v>277</v>
-      </c>
-      <c r="D42" s="6">
+        <v>207</v>
+      </c>
+      <c r="D42" s="2">
         <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A43" s="6">
+      <c r="A43" s="2">
         <v>42</v>
       </c>
       <c r="C43" t="s">
-        <v>277</v>
-      </c>
-      <c r="D43" s="6">
+        <v>207</v>
+      </c>
+      <c r="D43" s="2">
         <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A44" s="6">
+      <c r="A44" s="2">
         <v>43</v>
       </c>
       <c r="C44" t="s">
-        <v>277</v>
-      </c>
-      <c r="D44" s="6">
+        <v>207</v>
+      </c>
+      <c r="D44" s="2">
         <v>43</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A45" s="6">
+      <c r="A45" s="2">
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>294</v>
+        <v>220</v>
       </c>
       <c r="C45" t="s">
-        <v>277</v>
-      </c>
-      <c r="D45" s="6">
+        <v>207</v>
+      </c>
+      <c r="D45" s="2">
         <v>44</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A46" s="6">
+      <c r="A46" s="2">
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>295</v>
+        <v>221</v>
       </c>
       <c r="C46" t="s">
-        <v>277</v>
-      </c>
-      <c r="D46" s="6">
+        <v>207</v>
+      </c>
+      <c r="D46" s="2">
         <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A47" s="6">
+      <c r="A47" s="2">
         <v>46</v>
       </c>
       <c r="C47" t="s">
-        <v>277</v>
-      </c>
-      <c r="D47" s="6">
+        <v>207</v>
+      </c>
+      <c r="D47" s="2">
         <v>46</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A48" s="6">
+      <c r="A48" s="2">
         <v>47</v>
       </c>
       <c r="C48" t="s">
-        <v>277</v>
-      </c>
-      <c r="D48" s="6">
+        <v>207</v>
+      </c>
+      <c r="D48" s="2">
         <v>47</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A49" s="6">
+      <c r="A49" s="2">
         <v>48</v>
       </c>
       <c r="C49" t="s">
-        <v>277</v>
-      </c>
-      <c r="D49" s="6">
+        <v>207</v>
+      </c>
+      <c r="D49" s="2">
         <v>48</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A50" s="6">
+      <c r="A50" s="2">
         <v>49</v>
       </c>
       <c r="C50" t="s">
-        <v>277</v>
-      </c>
-      <c r="D50" s="6">
+        <v>207</v>
+      </c>
+      <c r="D50" s="2">
         <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A51" s="6">
+      <c r="A51" s="2">
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>296</v>
+        <v>222</v>
       </c>
       <c r="C51" t="s">
-        <v>277</v>
-      </c>
-      <c r="D51" s="6">
+        <v>207</v>
+      </c>
+      <c r="D51" s="2">
         <v>50</v>
       </c>
-      <c r="E51" s="6">
+      <c r="E51" s="2">
         <v>32</v>
       </c>
-      <c r="F51" s="6">
+      <c r="F51" s="2">
         <f>Table5[[#This Row],[G002 Output (VSC)]]+64</f>
         <v>96</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A52" s="6">
+      <c r="A52" s="2">
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>297</v>
+        <v>223</v>
       </c>
       <c r="C52" t="s">
-        <v>277</v>
-      </c>
-      <c r="D52" s="6">
+        <v>207</v>
+      </c>
+      <c r="D52" s="2">
         <v>51</v>
       </c>
-      <c r="E52" s="6">
+      <c r="E52" s="2">
         <v>33</v>
       </c>
-      <c r="F52" s="6">
+      <c r="F52" s="2">
         <f>Table5[[#This Row],[G002 Output (VSC)]]+64</f>
         <v>97</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A53" s="6">
+      <c r="A53" s="2">
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>298</v>
+        <v>224</v>
       </c>
       <c r="C53" t="s">
-        <v>277</v>
-      </c>
-      <c r="D53" s="6">
+        <v>207</v>
+      </c>
+      <c r="D53" s="2">
         <v>52</v>
       </c>
-      <c r="E53" s="6">
+      <c r="E53" s="2">
         <v>34</v>
       </c>
-      <c r="F53" s="6">
+      <c r="F53" s="2">
         <f>Table5[[#This Row],[G002 Output (VSC)]]+64</f>
         <v>98</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A54" s="6">
+      <c r="A54" s="2">
         <v>53</v>
       </c>
       <c r="C54" t="s">
-        <v>277</v>
-      </c>
-      <c r="D54" s="6">
+        <v>207</v>
+      </c>
+      <c r="D54" s="2">
         <v>53</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A55" s="6">
+      <c r="A55" s="2">
         <v>54</v>
       </c>
       <c r="C55" t="s">
-        <v>277</v>
-      </c>
-      <c r="D55" s="6">
+        <v>207</v>
+      </c>
+      <c r="D55" s="2">
         <v>54</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A56" s="6">
+      <c r="A56" s="2">
         <v>55</v>
       </c>
       <c r="C56" t="s">
-        <v>277</v>
-      </c>
-      <c r="D56" s="6">
+        <v>207</v>
+      </c>
+      <c r="D56" s="2">
         <v>55</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A57" s="6">
+      <c r="A57" s="2">
         <v>56</v>
       </c>
       <c r="C57" t="s">
-        <v>277</v>
-      </c>
-      <c r="D57" s="6">
+        <v>207</v>
+      </c>
+      <c r="D57" s="2">
         <v>56</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A58" s="6">
+      <c r="A58" s="2">
         <v>57</v>
       </c>
       <c r="C58" t="s">
-        <v>277</v>
-      </c>
-      <c r="D58" s="6">
+        <v>207</v>
+      </c>
+      <c r="D58" s="2">
         <v>57</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A59" s="6">
+      <c r="A59" s="2">
         <v>58</v>
       </c>
       <c r="C59" t="s">
-        <v>277</v>
-      </c>
-      <c r="D59" s="6">
+        <v>207</v>
+      </c>
+      <c r="D59" s="2">
         <v>58</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A60" s="6">
+      <c r="A60" s="2">
         <v>59</v>
       </c>
       <c r="C60" t="s">
-        <v>277</v>
-      </c>
-      <c r="D60" s="6">
+        <v>207</v>
+      </c>
+      <c r="D60" s="2">
         <v>59</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A61" s="6">
+      <c r="A61" s="2">
         <v>60</v>
       </c>
       <c r="C61" t="s">
-        <v>277</v>
-      </c>
-      <c r="D61" s="6">
+        <v>207</v>
+      </c>
+      <c r="D61" s="2">
         <v>60</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A62" s="6">
+      <c r="A62" s="2">
         <v>61</v>
       </c>
       <c r="C62" t="s">
-        <v>277</v>
-      </c>
-      <c r="D62" s="6">
+        <v>207</v>
+      </c>
+      <c r="D62" s="2">
         <v>61</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A63" s="6">
+      <c r="A63" s="2">
         <v>62</v>
       </c>
       <c r="C63" t="s">
-        <v>277</v>
-      </c>
-      <c r="D63" s="6">
+        <v>207</v>
+      </c>
+      <c r="D63" s="2">
         <v>62</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A64" s="6">
+      <c r="A64" s="2">
         <v>63</v>
       </c>
       <c r="C64" t="s">
-        <v>277</v>
-      </c>
-      <c r="D64" s="6">
+        <v>207</v>
+      </c>
+      <c r="D64" s="2">
         <v>63</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A65" s="6">
+      <c r="A65" s="2">
         <v>64</v>
       </c>
       <c r="C65" t="s">
-        <v>277</v>
-      </c>
-      <c r="D65" s="6">
+        <v>207</v>
+      </c>
+      <c r="D65" s="2">
         <v>64</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A66" s="6">
+      <c r="A66" s="2">
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>299</v>
+        <v>225</v>
       </c>
       <c r="C66" t="s">
-        <v>322</v>
-      </c>
-      <c r="D66" s="6">
+        <v>260</v>
+      </c>
+      <c r="D66" s="2">
         <v>1</v>
       </c>
-      <c r="E66" s="6">
+      <c r="E66" s="2">
         <v>1</v>
       </c>
-      <c r="F66" s="6">
+      <c r="F66" s="2">
         <v>65</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A67" s="6">
+      <c r="A67" s="2">
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>300</v>
+        <v>226</v>
       </c>
       <c r="C67" t="s">
-        <v>322</v>
-      </c>
-      <c r="D67" s="6">
-        <v>1</v>
-      </c>
-      <c r="E67" s="6">
+        <v>260</v>
+      </c>
+      <c r="D67" s="2">
         <v>2</v>
       </c>
-      <c r="F67" s="6">
+      <c r="E67" s="2">
+        <v>2</v>
+      </c>
+      <c r="F67" s="2">
         <v>66</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A68" s="6">
+      <c r="A68" s="2">
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>301</v>
+        <v>227</v>
       </c>
       <c r="C68" t="s">
-        <v>322</v>
-      </c>
-      <c r="D68" s="6">
-        <v>1</v>
-      </c>
-      <c r="E68" s="6">
+        <v>260</v>
+      </c>
+      <c r="D68" s="2">
         <v>3</v>
       </c>
-      <c r="F68" s="6">
+      <c r="E68" s="2">
+        <v>3</v>
+      </c>
+      <c r="F68" s="2">
         <v>67</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A69" s="6">
+      <c r="A69" s="2">
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>302</v>
+        <v>228</v>
       </c>
       <c r="C69" t="s">
-        <v>322</v>
-      </c>
-      <c r="D69" s="6">
-        <v>1</v>
-      </c>
-      <c r="E69" s="6">
+        <v>260</v>
+      </c>
+      <c r="D69" s="2">
         <v>4</v>
       </c>
-      <c r="F69" s="6">
+      <c r="E69" s="2">
+        <v>4</v>
+      </c>
+      <c r="F69" s="2">
         <v>68</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A70" s="6">
+      <c r="A70" s="2">
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>303</v>
+        <v>229</v>
       </c>
       <c r="C70" t="s">
-        <v>322</v>
-      </c>
-      <c r="D70" s="6">
-        <v>1</v>
-      </c>
-      <c r="E70" s="6">
-        <v>5</v>
-      </c>
-      <c r="F70" s="6">
+        <v>260</v>
+      </c>
+      <c r="D70" s="2">
+        <v>5</v>
+      </c>
+      <c r="E70" s="2">
+        <v>5</v>
+      </c>
+      <c r="F70" s="2">
         <v>69</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A71" s="6">
+      <c r="A71" s="2">
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>304</v>
+        <v>230</v>
       </c>
       <c r="C71" t="s">
-        <v>322</v>
-      </c>
-      <c r="D71" s="6">
-        <v>1</v>
-      </c>
-      <c r="E71" s="6">
+        <v>260</v>
+      </c>
+      <c r="D71" s="2">
         <v>6</v>
       </c>
-      <c r="F71" s="6">
+      <c r="E71" s="2">
+        <v>6</v>
+      </c>
+      <c r="F71" s="2">
         <v>70</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A72" s="6">
+      <c r="A72" s="2">
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>305</v>
+        <v>231</v>
       </c>
       <c r="C72" t="s">
-        <v>322</v>
-      </c>
-      <c r="D72" s="6">
-        <v>1</v>
-      </c>
-      <c r="E72" s="6">
+        <v>260</v>
+      </c>
+      <c r="D72" s="2">
         <v>7</v>
       </c>
-      <c r="F72" s="6">
+      <c r="E72" s="2">
+        <v>7</v>
+      </c>
+      <c r="F72" s="2">
         <v>71</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A73" s="6">
+      <c r="A73" s="2">
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>306</v>
+        <v>232</v>
       </c>
       <c r="C73" t="s">
-        <v>322</v>
-      </c>
-      <c r="D73" s="6">
-        <v>1</v>
-      </c>
-      <c r="E73" s="6">
+        <v>260</v>
+      </c>
+      <c r="D73" s="2">
         <v>8</v>
       </c>
-      <c r="F73" s="6">
+      <c r="E73" s="2">
+        <v>8</v>
+      </c>
+      <c r="F73" s="2">
         <v>72</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A74" s="6">
+      <c r="A74" s="2">
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>307</v>
+        <v>233</v>
       </c>
       <c r="C74" t="s">
-        <v>322</v>
-      </c>
-      <c r="D74" s="6">
-        <v>1</v>
-      </c>
-      <c r="E74" s="6">
+        <v>260</v>
+      </c>
+      <c r="D74" s="2">
         <v>9</v>
       </c>
-      <c r="F74" s="6">
+      <c r="E74" s="2">
+        <v>9</v>
+      </c>
+      <c r="F74" s="2">
         <v>73</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A75" s="6">
+      <c r="A75" s="2">
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>308</v>
+        <v>234</v>
       </c>
       <c r="C75" t="s">
-        <v>322</v>
-      </c>
-      <c r="D75" s="6">
-        <v>1</v>
-      </c>
-      <c r="E75" s="6">
+        <v>260</v>
+      </c>
+      <c r="D75" s="2">
         <v>10</v>
       </c>
-      <c r="F75" s="6">
+      <c r="E75" s="2">
+        <v>10</v>
+      </c>
+      <c r="F75" s="2">
         <v>74</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A76" s="6">
+      <c r="A76" s="2">
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>309</v>
+        <v>235</v>
       </c>
       <c r="C76" t="s">
-        <v>322</v>
-      </c>
-      <c r="D76" s="6">
-        <v>1</v>
-      </c>
-      <c r="E76" s="6">
+        <v>260</v>
+      </c>
+      <c r="D76" s="2">
         <v>11</v>
       </c>
-      <c r="F76" s="6">
+      <c r="E76" s="2">
+        <v>11</v>
+      </c>
+      <c r="F76" s="2">
         <v>75</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A77" s="6">
+      <c r="A77" s="2">
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>310</v>
+        <v>236</v>
       </c>
       <c r="C77" t="s">
-        <v>322</v>
-      </c>
-      <c r="D77" s="6">
-        <v>1</v>
-      </c>
-      <c r="E77" s="6">
+        <v>260</v>
+      </c>
+      <c r="D77" s="2">
         <v>12</v>
       </c>
-      <c r="F77" s="6">
+      <c r="E77" s="2">
+        <v>12</v>
+      </c>
+      <c r="F77" s="2">
         <v>76</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A78" s="6">
+      <c r="A78" s="2">
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>311</v>
+        <v>237</v>
       </c>
       <c r="C78" t="s">
-        <v>322</v>
-      </c>
-      <c r="D78" s="6">
-        <v>1</v>
-      </c>
-      <c r="E78" s="6">
+        <v>260</v>
+      </c>
+      <c r="D78" s="2">
         <v>13</v>
       </c>
-      <c r="F78" s="6">
+      <c r="E78" s="2">
+        <v>13</v>
+      </c>
+      <c r="F78" s="2">
         <v>77</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A79" s="6">
+      <c r="A79" s="2">
         <v>78</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A80" s="6">
+      <c r="A80" s="2">
         <v>79</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A81" s="6">
+      <c r="A81" s="2">
         <v>80</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A82" s="6">
+      <c r="A82" s="2">
         <v>81</v>
       </c>
       <c r="B82" t="s">
         <v>98</v>
       </c>
       <c r="C82" t="s">
-        <v>321</v>
-      </c>
-      <c r="D82" s="6">
-        <v>1</v>
-      </c>
-      <c r="E82" s="6">
+        <v>261</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="E82" s="2">
         <v>41</v>
       </c>
-      <c r="F82" s="6">
+      <c r="F82" s="2">
         <f>Table5[[#This Row],[G002 Output (VSC)]]+64</f>
         <v>105</v>
       </c>
-      <c r="G82" s="6">
+      <c r="G82" s="2">
         <v>46</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A83" s="6">
+      <c r="A83" s="2">
         <v>82</v>
       </c>
       <c r="B83" t="s">
         <v>99</v>
       </c>
       <c r="C83" t="s">
-        <v>321</v>
-      </c>
-      <c r="D83" s="6">
-        <v>2</v>
-      </c>
-      <c r="E83" s="6">
+        <v>261</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="E83" s="2">
         <v>42</v>
       </c>
-      <c r="F83" s="6">
+      <c r="F83" s="2">
         <f>Table5[[#This Row],[G002 Output (VSC)]]+64</f>
         <v>106</v>
       </c>
-      <c r="G83" s="6">
+      <c r="G83" s="2">
         <v>47</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A84" s="6">
+      <c r="A84" s="2">
         <v>83</v>
       </c>
       <c r="B84" t="s">
         <v>100</v>
       </c>
       <c r="C84" t="s">
-        <v>321</v>
-      </c>
-      <c r="D84" s="6">
-        <v>3</v>
-      </c>
-      <c r="E84" s="6">
+        <v>261</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="E84" s="2">
         <v>43</v>
       </c>
-      <c r="F84" s="6">
+      <c r="F84" s="2">
         <f>Table5[[#This Row],[G002 Output (VSC)]]+64</f>
         <v>107</v>
       </c>
-      <c r="G84" s="6">
+      <c r="G84" s="2">
         <v>48</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A85" s="6">
+      <c r="A85" s="2">
         <v>84</v>
       </c>
       <c r="B85" t="s">
         <v>101</v>
       </c>
       <c r="C85" t="s">
-        <v>321</v>
-      </c>
-      <c r="D85" s="6">
-        <v>4</v>
-      </c>
-      <c r="E85" s="6">
+        <v>261</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="E85" s="2">
         <v>44</v>
       </c>
-      <c r="F85" s="6">
+      <c r="F85" s="2">
         <f>Table5[[#This Row],[G002 Output (VSC)]]+64</f>
         <v>108</v>
       </c>
-      <c r="G85" s="6">
+      <c r="G85" s="2">
         <v>49</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A86" s="6">
+      <c r="A86" s="2">
         <v>85</v>
       </c>
       <c r="B86" t="s">
         <v>102</v>
       </c>
       <c r="C86" t="s">
-        <v>321</v>
-      </c>
-      <c r="D86" s="6">
-        <v>5</v>
-      </c>
-      <c r="E86" s="6">
+        <v>261</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="E86" s="2">
         <v>45</v>
       </c>
-      <c r="F86" s="6">
+      <c r="F86" s="2">
         <f>Table5[[#This Row],[G002 Output (VSC)]]+64</f>
         <v>109</v>
       </c>
-      <c r="G86" s="6">
+      <c r="G86" s="2">
         <v>50</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A87" s="6">
+      <c r="A87" s="2">
         <v>86</v>
       </c>
       <c r="B87" t="s">
         <v>103</v>
       </c>
       <c r="C87" t="s">
-        <v>321</v>
-      </c>
-      <c r="D87" s="6">
-        <v>6</v>
-      </c>
-      <c r="E87" s="6">
+        <v>261</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="E87" s="2">
         <v>46</v>
       </c>
-      <c r="F87" s="6">
+      <c r="F87" s="2">
         <f>Table5[[#This Row],[G002 Output (VSC)]]+64</f>
         <v>110</v>
       </c>
-      <c r="G87" s="6">
+      <c r="G87" s="2">
         <v>51</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A88" s="6">
+      <c r="A88" s="2">
         <v>87</v>
       </c>
       <c r="B88" t="s">
         <v>104</v>
       </c>
       <c r="C88" t="s">
-        <v>321</v>
-      </c>
-      <c r="D88" s="6">
-        <v>7</v>
-      </c>
-      <c r="E88" s="6">
+        <v>261</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="E88" s="2">
         <v>47</v>
       </c>
-      <c r="F88" s="6">
+      <c r="F88" s="2">
         <f>Table5[[#This Row],[G002 Output (VSC)]]+64</f>
         <v>111</v>
       </c>
-      <c r="G88" s="6">
+      <c r="G88" s="2">
         <v>52</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A89" s="6">
+      <c r="A89" s="2">
         <v>88</v>
       </c>
       <c r="B89" t="s">
         <v>105</v>
       </c>
       <c r="C89" t="s">
-        <v>321</v>
-      </c>
-      <c r="D89" s="6">
-        <v>8</v>
-      </c>
-      <c r="E89" s="6">
+        <v>261</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="E89" s="2">
         <v>48</v>
       </c>
-      <c r="F89" s="6">
+      <c r="F89" s="2">
         <f>Table5[[#This Row],[G002 Output (VSC)]]+64</f>
         <v>112</v>
       </c>
-      <c r="G89" s="6">
+      <c r="G89" s="2">
         <v>53</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A90" s="6">
+      <c r="A90" s="2">
         <v>89</v>
       </c>
       <c r="B90" t="s">
         <v>106</v>
       </c>
       <c r="C90" t="s">
-        <v>321</v>
-      </c>
-      <c r="D90" s="6">
-        <v>9</v>
-      </c>
-      <c r="E90" s="6">
+        <v>261</v>
+      </c>
+      <c r="D90" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="E90" s="2">
         <v>49</v>
       </c>
-      <c r="F90" s="6">
+      <c r="F90" s="2">
         <f>Table5[[#This Row],[G002 Output (VSC)]]+64</f>
         <v>113</v>
       </c>
-      <c r="G90" s="6">
+      <c r="G90" s="2">
         <v>54</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A91" s="6">
+      <c r="A91" s="2">
         <v>90</v>
       </c>
       <c r="B91" t="s">
         <v>107</v>
       </c>
       <c r="C91" t="s">
-        <v>321</v>
-      </c>
-      <c r="D91" s="6">
+        <v>261</v>
+      </c>
+      <c r="D91" s="2">
         <v>10</v>
       </c>
-      <c r="E91" s="6">
+      <c r="E91" s="2">
         <v>50</v>
       </c>
-      <c r="F91" s="6">
+      <c r="F91" s="2">
         <f>Table5[[#This Row],[G002 Output (VSC)]]+64</f>
         <v>114</v>
       </c>
-      <c r="G91" s="6">
+      <c r="G91" s="2">
         <v>55</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A92" s="6">
+      <c r="A92" s="2">
         <v>91</v>
       </c>
       <c r="B92" t="s">
         <v>108</v>
       </c>
       <c r="C92" t="s">
-        <v>321</v>
-      </c>
-      <c r="D92" s="6">
+        <v>261</v>
+      </c>
+      <c r="D92" s="2">
         <v>11</v>
       </c>
-      <c r="E92" s="6">
+      <c r="E92" s="2">
         <v>51</v>
       </c>
-      <c r="F92" s="6">
+      <c r="F92" s="2">
         <f>Table5[[#This Row],[G002 Output (VSC)]]+64</f>
         <v>115</v>
       </c>
-      <c r="G92" s="13"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A93" s="6">
+      <c r="A93" s="2">
         <v>92</v>
       </c>
       <c r="B93" t="s">
         <v>109</v>
       </c>
       <c r="C93" t="s">
-        <v>321</v>
-      </c>
-      <c r="D93" s="6">
+        <v>261</v>
+      </c>
+      <c r="D93" s="2">
         <v>12</v>
       </c>
-      <c r="E93" s="6">
+      <c r="E93" s="2">
         <v>52</v>
       </c>
-      <c r="F93" s="6">
+      <c r="F93" s="2">
         <f>Table5[[#This Row],[G002 Output (VSC)]]+64</f>
         <v>116</v>
       </c>
-      <c r="G93" s="13"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A94" s="6">
+      <c r="A94" s="2">
         <v>93</v>
       </c>
       <c r="B94" t="s">
         <v>110</v>
       </c>
       <c r="C94" t="s">
-        <v>321</v>
-      </c>
-      <c r="D94" s="6">
+        <v>261</v>
+      </c>
+      <c r="D94" s="2">
         <v>13</v>
       </c>
-      <c r="E94" s="6">
+      <c r="E94" s="2">
         <v>53</v>
       </c>
-      <c r="F94" s="6">
+      <c r="F94" s="2">
         <f>Table5[[#This Row],[G002 Output (VSC)]]+64</f>
         <v>117</v>
       </c>
-      <c r="G94" s="13"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A95" s="6">
+      <c r="A95" s="2">
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>312</v>
+        <v>238</v>
       </c>
       <c r="C95" t="s">
-        <v>321</v>
-      </c>
-      <c r="D95" s="6">
+        <v>261</v>
+      </c>
+      <c r="D95" s="2">
         <v>14</v>
       </c>
-      <c r="E95" s="6">
+      <c r="E95" s="2">
         <v>54</v>
       </c>
-      <c r="F95" s="6">
+      <c r="F95" s="2">
         <f>Table5[[#This Row],[G002 Output (VSC)]]+64</f>
         <v>118</v>
       </c>
-      <c r="G95" s="13"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A96" s="6">
+      <c r="A96" s="2">
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>313</v>
+        <v>239</v>
       </c>
       <c r="C96" t="s">
-        <v>321</v>
-      </c>
-      <c r="D96" s="6">
+        <v>261</v>
+      </c>
+      <c r="D96" s="2">
         <v>15</v>
       </c>
-      <c r="E96" s="6">
+      <c r="E96" s="2">
         <v>55</v>
       </c>
-      <c r="F96" s="6">
+      <c r="F96" s="2">
         <f>Table5[[#This Row],[G002 Output (VSC)]]+64</f>
         <v>119</v>
       </c>
-      <c r="G96" s="13"/>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A97" s="6">
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A97" s="2">
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>252</v>
+        <v>182</v>
       </c>
       <c r="C97" t="s">
-        <v>321</v>
-      </c>
-      <c r="D97" s="6">
+        <v>261</v>
+      </c>
+      <c r="D97" s="2">
         <v>16</v>
       </c>
-      <c r="E97" s="6">
+      <c r="E97" s="2">
         <v>56</v>
       </c>
-      <c r="F97" s="6">
+      <c r="F97" s="2">
         <f>Table5[[#This Row],[G002 Output (VSC)]]+64</f>
         <v>120</v>
       </c>
-      <c r="G97" s="13"/>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A98" s="6">
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B98" t="s">
+        <v>225</v>
+      </c>
+      <c r="C98" t="s">
+        <v>261</v>
+      </c>
+      <c r="D98" s="2">
+        <v>65</v>
+      </c>
+      <c r="F98" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B99" t="s">
+        <v>226</v>
+      </c>
+      <c r="C99" t="s">
+        <v>261</v>
+      </c>
+      <c r="D99" s="2">
+        <v>66</v>
+      </c>
+      <c r="F99" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B100" t="s">
+        <v>227</v>
+      </c>
+      <c r="C100" t="s">
+        <v>261</v>
+      </c>
+      <c r="D100" s="2">
+        <v>67</v>
+      </c>
+      <c r="F100" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B101" t="s">
+        <v>228</v>
+      </c>
+      <c r="C101" t="s">
+        <v>261</v>
+      </c>
+      <c r="D101" s="2">
+        <v>68</v>
+      </c>
+      <c r="F101" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B102" t="s">
+        <v>229</v>
+      </c>
+      <c r="C102" t="s">
+        <v>261</v>
+      </c>
+      <c r="D102" s="2">
+        <v>69</v>
+      </c>
+      <c r="F102" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B103" t="s">
+        <v>230</v>
+      </c>
+      <c r="C103" t="s">
+        <v>261</v>
+      </c>
+      <c r="D103" s="2">
+        <v>70</v>
+      </c>
+      <c r="F103" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B104" t="s">
+        <v>231</v>
+      </c>
+      <c r="C104" t="s">
+        <v>261</v>
+      </c>
+      <c r="D104" s="2">
+        <v>71</v>
+      </c>
+      <c r="F104" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B105" t="s">
+        <v>232</v>
+      </c>
+      <c r="C105" t="s">
+        <v>261</v>
+      </c>
+      <c r="D105" s="2">
+        <v>72</v>
+      </c>
+      <c r="F105" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B106" t="s">
+        <v>233</v>
+      </c>
+      <c r="C106" t="s">
+        <v>261</v>
+      </c>
+      <c r="D106" s="2">
+        <v>73</v>
+      </c>
+      <c r="F106" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B107" t="s">
+        <v>234</v>
+      </c>
+      <c r="C107" t="s">
+        <v>261</v>
+      </c>
+      <c r="D107" s="2">
+        <v>74</v>
+      </c>
+      <c r="F107" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B108" t="s">
+        <v>235</v>
+      </c>
+      <c r="C108" t="s">
+        <v>261</v>
+      </c>
+      <c r="D108" s="2">
+        <v>75</v>
+      </c>
+      <c r="F108" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B109" t="s">
+        <v>236</v>
+      </c>
+      <c r="C109" t="s">
+        <v>261</v>
+      </c>
+      <c r="D109" s="2">
+        <v>76</v>
+      </c>
+      <c r="F109" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C110" t="s">
+        <v>261</v>
+      </c>
+      <c r="D110" s="2">
+        <v>77</v>
+      </c>
+      <c r="F110" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C111" t="s">
+        <v>261</v>
+      </c>
+      <c r="D111" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C112" t="s">
+        <v>261</v>
+      </c>
+      <c r="D112" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="113" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C113" t="s">
+        <v>261</v>
+      </c>
+      <c r="D113" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="114" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C114" t="s">
+        <v>261</v>
+      </c>
+      <c r="D114" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="115" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C115" t="s">
+        <v>261</v>
+      </c>
+      <c r="D115" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="116" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C116" t="s">
+        <v>261</v>
+      </c>
+      <c r="D116" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="117" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C117" t="s">
+        <v>261</v>
+      </c>
+      <c r="D117" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="118" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C118" t="s">
+        <v>261</v>
+      </c>
+      <c r="D118" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="119" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C119" t="s">
+        <v>261</v>
+      </c>
+      <c r="D119" s="2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="120" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C120" t="s">
+        <v>261</v>
+      </c>
+      <c r="D120" s="2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="121" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C121" t="s">
+        <v>261</v>
+      </c>
+      <c r="D121" s="2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="122" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C122" t="s">
+        <v>261</v>
+      </c>
+      <c r="D122" s="2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="123" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C123" t="s">
+        <v>261</v>
+      </c>
+      <c r="D123" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="124" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C124" t="s">
+        <v>261</v>
+      </c>
+      <c r="D124" s="2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="125" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C125" t="s">
+        <v>261</v>
+      </c>
+      <c r="D125" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="126" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C126" t="s">
+        <v>261</v>
+      </c>
+      <c r="D126" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="127" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C127" t="s">
+        <v>261</v>
+      </c>
+      <c r="D127" s="2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="128" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C128" t="s">
+        <v>261</v>
+      </c>
+      <c r="D128" s="2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="129" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C129" t="s">
+        <v>261</v>
+      </c>
+      <c r="D129" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="130" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C130" t="s">
+        <v>261</v>
+      </c>
+      <c r="D130" s="2">
         <v>97</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A99" s="6">
+    <row r="131" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C131" t="s">
+        <v>261</v>
+      </c>
+      <c r="D131" s="2">
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A100" s="6">
+    <row r="132" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C132" t="s">
+        <v>261</v>
+      </c>
+      <c r="D132" s="2">
         <v>99</v>
       </c>
-      <c r="B100" t="s">
-        <v>326</v>
-      </c>
-      <c r="C100" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A101" s="6">
+    </row>
+    <row r="133" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C133" t="s">
+        <v>261</v>
+      </c>
+      <c r="D133" s="2">
         <v>100</v>
       </c>
-      <c r="B101" t="s">
-        <v>314</v>
-      </c>
-      <c r="C101" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A102" s="6">
+    </row>
+    <row r="134" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C134" t="s">
+        <v>261</v>
+      </c>
+      <c r="D134" s="2">
         <v>101</v>
       </c>
-      <c r="B102" t="s">
-        <v>315</v>
-      </c>
-      <c r="C102" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A103" s="6">
+    </row>
+    <row r="135" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C135" t="s">
+        <v>261</v>
+      </c>
+      <c r="D135" s="2">
         <v>102</v>
       </c>
-      <c r="B103" t="s">
-        <v>316</v>
-      </c>
-      <c r="C103" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A104" s="6">
+    </row>
+    <row r="136" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C136" t="s">
+        <v>261</v>
+      </c>
+      <c r="D136" s="2">
         <v>103</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A105" s="6">
+    <row r="137" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C137" t="s">
+        <v>261</v>
+      </c>
+      <c r="D137" s="2">
         <v>104</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A106" s="6">
+    <row r="138" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C138" t="s">
+        <v>261</v>
+      </c>
+      <c r="D138" s="2">
         <v>105</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A107" s="6">
+    <row r="139" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C139" t="s">
+        <v>261</v>
+      </c>
+      <c r="D139" s="2">
         <v>106</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A108" s="6">
+    <row r="140" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C140" t="s">
+        <v>261</v>
+      </c>
+      <c r="D140" s="2">
         <v>107</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A109" s="6">
+    <row r="141" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C141" t="s">
+        <v>261</v>
+      </c>
+      <c r="D141" s="2">
         <v>108</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A110" s="6">
+    <row r="142" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C142" t="s">
+        <v>261</v>
+      </c>
+      <c r="D142" s="2">
         <v>109</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A111" s="6">
+    <row r="143" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C143" t="s">
+        <v>261</v>
+      </c>
+      <c r="D143" s="2">
         <v>110</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A112" s="6">
+    <row r="144" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C144" t="s">
+        <v>261</v>
+      </c>
+      <c r="D144" s="2">
         <v>111</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A113" s="6">
+    <row r="145" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C145" t="s">
+        <v>261</v>
+      </c>
+      <c r="D145" s="2">
         <v>112</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A114" s="6">
+    <row r="146" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C146" t="s">
+        <v>261</v>
+      </c>
+      <c r="D146" s="2">
         <v>113</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A115" s="6">
+    <row r="147" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C147" t="s">
+        <v>261</v>
+      </c>
+      <c r="D147" s="2">
         <v>114</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A116" s="6">
+    <row r="148" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C148" t="s">
+        <v>261</v>
+      </c>
+      <c r="D148" s="2">
         <v>115</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A117" s="6">
+    <row r="149" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C149" t="s">
+        <v>261</v>
+      </c>
+      <c r="D149" s="2">
         <v>116</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A118" s="6">
+    <row r="150" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C150" t="s">
+        <v>261</v>
+      </c>
+      <c r="D150" s="2">
         <v>117</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A119" s="6">
+    <row r="151" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C151" t="s">
+        <v>261</v>
+      </c>
+      <c r="D151" s="2">
         <v>118</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A120" s="6">
+    <row r="152" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C152" t="s">
+        <v>261</v>
+      </c>
+      <c r="D152" s="2">
         <v>119</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A121" s="6">
+    <row r="153" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C153" t="s">
+        <v>261</v>
+      </c>
+      <c r="D153" s="2">
         <v>120</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A122" s="6">
+    <row r="154" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C154" t="s">
+        <v>261</v>
+      </c>
+      <c r="D154" s="2">
         <v>121</v>
       </c>
-      <c r="B122" t="s">
+    </row>
+    <row r="155" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C155" t="s">
+        <v>261</v>
+      </c>
+      <c r="D155" s="2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="156" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C156" t="s">
+        <v>261</v>
+      </c>
+      <c r="D156" s="2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="157" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C157" t="s">
+        <v>261</v>
+      </c>
+      <c r="D157" s="2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="158" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C158" t="s">
+        <v>261</v>
+      </c>
+      <c r="D158" s="2">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="159" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C159" t="s">
+        <v>261</v>
+      </c>
+      <c r="D159" s="2">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="160" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C160" t="s">
+        <v>261</v>
+      </c>
+      <c r="D160" s="2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C161" t="s">
+        <v>261</v>
+      </c>
+      <c r="D161" s="2">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A162" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A163" s="2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A164" s="2">
+        <v>99</v>
+      </c>
+      <c r="B164" t="s">
+        <v>249</v>
+      </c>
+      <c r="C164" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A165" s="2">
+        <v>100</v>
+      </c>
+      <c r="B165" t="s">
+        <v>240</v>
+      </c>
+      <c r="C165" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A166" s="2">
+        <v>101</v>
+      </c>
+      <c r="B166" t="s">
+        <v>241</v>
+      </c>
+      <c r="C166" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A167" s="2">
+        <v>102</v>
+      </c>
+      <c r="B167" t="s">
+        <v>242</v>
+      </c>
+      <c r="C167" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A168" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A169" s="2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A170" s="2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A171" s="2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A172" s="2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A173" s="2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A174" s="2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A175" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A176" s="2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A177" s="2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A178" s="2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A179" s="2">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A180" s="2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A181" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A182" s="2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A183" s="2">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A184" s="2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A185" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A186" s="2">
+        <v>121</v>
+      </c>
+      <c r="B186" t="s">
         <v>84</v>
       </c>
-      <c r="C122" t="s">
-        <v>323</v>
-      </c>
-      <c r="D122" s="6" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A123" s="6">
+      <c r="C186" t="s">
+        <v>247</v>
+      </c>
+      <c r="D186" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A187" s="2">
         <v>122</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B187" t="s">
         <v>85</v>
       </c>
-      <c r="C123" t="s">
-        <v>323</v>
-      </c>
-      <c r="D123" s="6" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A124" s="6">
+      <c r="C187" t="s">
+        <v>247</v>
+      </c>
+      <c r="D187" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A188" s="2">
         <v>123</v>
       </c>
-      <c r="B124" t="s">
-        <v>317</v>
-      </c>
-      <c r="C124" t="s">
-        <v>323</v>
-      </c>
-      <c r="D124" s="6" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A125" s="6">
+      <c r="B188" t="s">
+        <v>243</v>
+      </c>
+      <c r="C188" t="s">
+        <v>247</v>
+      </c>
+      <c r="D188" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A189" s="2">
         <v>124</v>
       </c>
-      <c r="B125" t="s">
-        <v>318</v>
-      </c>
-      <c r="C125" t="s">
-        <v>323</v>
-      </c>
-      <c r="D125" s="6" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A126" s="6">
+      <c r="B189" t="s">
+        <v>244</v>
+      </c>
+      <c r="C189" t="s">
+        <v>247</v>
+      </c>
+      <c r="D189" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A190" s="2">
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A127" s="6">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A191" s="2">
         <v>126</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A128" s="6">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A192" s="2">
         <v>127</v>
       </c>
-      <c r="B128" t="s">
-        <v>319</v>
-      </c>
-      <c r="C128" t="s">
-        <v>323</v>
-      </c>
-      <c r="D128" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="E128" s="6">
+      <c r="B192" t="s">
+        <v>245</v>
+      </c>
+      <c r="C192" t="s">
+        <v>247</v>
+      </c>
+      <c r="D192" s="2">
+        <v>7</v>
+      </c>
+      <c r="E192" s="2">
         <v>63</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A129" s="6">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A193" s="2">
         <v>128</v>
       </c>
-      <c r="B129" t="s">
-        <v>320</v>
-      </c>
-      <c r="C129" t="s">
-        <v>323</v>
-      </c>
-      <c r="D129" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="E129" s="6">
+      <c r="B193" t="s">
+        <v>246</v>
+      </c>
+      <c r="C193" t="s">
+        <v>247</v>
+      </c>
+      <c r="D193" s="2">
+        <v>8</v>
+      </c>
+      <c r="E193" s="2">
         <v>64</v>
       </c>
     </row>
@@ -4948,676 +5246,388 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB4C5A61-7CDD-5C42-B217-B8E89E241867}">
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="11.6640625" customWidth="1"/>
-    <col min="3" max="3" width="14.1640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.83203125" customWidth="1"/>
-    <col min="7" max="7" width="17.6640625" customWidth="1"/>
-    <col min="8" max="8" width="24.5" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" style="12"/>
+    <col min="4" max="4" width="21.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
-        <v>214</v>
-      </c>
-      <c r="C1" s="9" t="s">
+      <c r="B1" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="C1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B2" s="13">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B3" s="13">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
         <v>132</v>
       </c>
-      <c r="D1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" t="s">
-        <v>161</v>
-      </c>
-      <c r="G1" t="s">
-        <v>119</v>
-      </c>
-      <c r="H1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="D2" t="s">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B4" s="13">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
         <v>133</v>
       </c>
-      <c r="E2" t="s">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B5" s="13">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="D3" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B6" s="13">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
         <v>135</v>
       </c>
-      <c r="E3" t="s">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B7" s="13">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="D4" t="s">
-        <v>139</v>
-      </c>
-      <c r="E4" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="D5" t="s">
-        <v>142</v>
-      </c>
-      <c r="E5" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="D6" t="s">
-        <v>145</v>
-      </c>
-      <c r="E6" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="D7" t="s">
-        <v>148</v>
-      </c>
-      <c r="E7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="E8" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+        <v>207</v>
+      </c>
+      <c r="B8" s="13">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="E9" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+        <v>207</v>
+      </c>
+      <c r="B9" s="13">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="E10" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+        <v>207</v>
+      </c>
+      <c r="B10" s="13">
+        <v>63</v>
+      </c>
+      <c r="C10" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C11" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="B11" s="13">
+        <v>64</v>
+      </c>
+      <c r="C11" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C12" s="9" t="s">
+      <c r="B12" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="C12" t="s">
         <v>154</v>
       </c>
-      <c r="D12" t="s">
-        <v>217</v>
-      </c>
-      <c r="F12">
-        <v>2</v>
-      </c>
-      <c r="G12" t="s">
-        <v>123</v>
-      </c>
-      <c r="H12">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D12" t="str">
+        <f>C12</f>
+        <v>Stream L</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C13" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="C13" t="s">
         <v>155</v>
       </c>
-      <c r="D13" t="s">
-        <v>218</v>
-      </c>
-      <c r="F13">
-        <v>2</v>
-      </c>
-      <c r="G13" t="s">
-        <v>123</v>
-      </c>
-      <c r="H13">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D13" t="str">
+        <f t="shared" ref="D13:D15" si="0">C13</f>
+        <v>Stream R</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C14" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="C14" t="s">
         <v>156</v>
       </c>
-      <c r="D14" t="s">
-        <v>219</v>
-      </c>
-      <c r="F14">
-        <v>2</v>
-      </c>
-      <c r="G14" t="s">
-        <v>123</v>
-      </c>
-      <c r="H14">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="D15" t="s">
-        <v>220</v>
-      </c>
-      <c r="F15">
-        <v>2</v>
-      </c>
-      <c r="G15" t="s">
-        <v>123</v>
-      </c>
-      <c r="H15">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="D16" t="s">
-        <v>221</v>
-      </c>
-      <c r="F16">
-        <v>2</v>
-      </c>
-      <c r="G16" t="s">
-        <v>123</v>
-      </c>
-      <c r="H16">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="D17" t="s">
-        <v>222</v>
-      </c>
-      <c r="F17">
-        <v>2</v>
-      </c>
-      <c r="G17" t="s">
-        <v>123</v>
-      </c>
-      <c r="H17">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="D18" t="s">
-        <v>98</v>
-      </c>
-      <c r="F18">
-        <v>2</v>
-      </c>
-      <c r="G18" t="s">
-        <v>123</v>
-      </c>
-      <c r="H18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="D19" t="s">
-        <v>99</v>
-      </c>
-      <c r="F19">
-        <v>2</v>
-      </c>
-      <c r="G19" t="s">
-        <v>123</v>
-      </c>
-      <c r="H19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="D20" t="s">
-        <v>100</v>
-      </c>
-      <c r="F20">
-        <v>2</v>
-      </c>
-      <c r="G20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H20">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="D21" t="s">
-        <v>101</v>
-      </c>
-      <c r="F21">
-        <v>2</v>
-      </c>
-      <c r="G21" t="s">
-        <v>123</v>
-      </c>
-      <c r="H21">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="D22" t="s">
-        <v>102</v>
-      </c>
-      <c r="F22">
-        <v>2</v>
-      </c>
-      <c r="G22" t="s">
-        <v>123</v>
-      </c>
-      <c r="H22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="D23" t="s">
-        <v>103</v>
-      </c>
-      <c r="F23">
-        <v>2</v>
-      </c>
-      <c r="G23" t="s">
-        <v>123</v>
-      </c>
-      <c r="H23">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="D24" t="s">
-        <v>104</v>
-      </c>
-      <c r="F24">
-        <v>2</v>
-      </c>
-      <c r="G24" t="s">
-        <v>123</v>
-      </c>
-      <c r="H24">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="D25" t="s">
-        <v>105</v>
-      </c>
-      <c r="F25">
-        <v>2</v>
-      </c>
-      <c r="G25" t="s">
-        <v>123</v>
-      </c>
-      <c r="H25">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="D26" t="s">
-        <v>106</v>
-      </c>
-      <c r="F26">
-        <v>2</v>
-      </c>
-      <c r="G26" t="s">
-        <v>123</v>
-      </c>
-      <c r="H26">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="D27" t="s">
-        <v>107</v>
-      </c>
-      <c r="F27">
-        <v>2</v>
-      </c>
-      <c r="G27" t="s">
-        <v>123</v>
-      </c>
-      <c r="H27">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C28" s="9">
-        <v>1</v>
-      </c>
-      <c r="D28" t="s">
-        <v>224</v>
-      </c>
-      <c r="E28" t="str">
-        <f>D28</f>
-        <v>Stream L</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C29" s="9">
-        <v>2</v>
-      </c>
-      <c r="D29" t="s">
-        <v>225</v>
-      </c>
-      <c r="E29" t="str">
-        <f t="shared" ref="E29:E33" si="0">D29</f>
-        <v>Stream R</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C30" s="9">
-        <v>3</v>
-      </c>
-      <c r="D30" t="s">
-        <v>226</v>
-      </c>
-      <c r="E30" t="str">
+      <c r="D14" t="str">
         <f t="shared" si="0"/>
         <v>RefMon L</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C31" s="9">
-        <v>4</v>
-      </c>
-      <c r="D31" t="s">
-        <v>227</v>
-      </c>
-      <c r="E31" t="str">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="C15" t="s">
+        <v>157</v>
+      </c>
+      <c r="D15" t="str">
         <f t="shared" si="0"/>
         <v>RefMon R</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C32" s="9">
-        <v>1</v>
-      </c>
-      <c r="D32" t="s">
-        <v>228</v>
-      </c>
-      <c r="E32" t="str">
-        <f t="shared" si="0"/>
-        <v>Left</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C33" s="9">
-        <v>2</v>
-      </c>
-      <c r="D33" t="s">
-        <v>229</v>
-      </c>
-      <c r="E33" t="str">
-        <f t="shared" si="0"/>
-        <v>Right</v>
-      </c>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="D16" s="11"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="D17" s="10"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="D18" s="11"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>265</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D19" s="10"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="D20" s="11"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="D21" s="10"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D22" s="11"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>265</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D23" s="10"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="D24" s="11"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="D25" s="10"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D26" s="11"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>265</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D27" s="10"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="D28" s="11"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="D29" s="10"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="D30" s="11"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>265</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="D31" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -5654,7 +5664,7 @@
         <v>91</v>
       </c>
       <c r="E1" t="s">
-        <v>232</v>
+        <v>162</v>
       </c>
       <c r="F1" t="s">
         <v>92</v>
@@ -5677,7 +5687,7 @@
         <v>97</v>
       </c>
       <c r="E2" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F2" t="s">
         <v>98</v>
@@ -5700,7 +5710,7 @@
         <v>97</v>
       </c>
       <c r="E3" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F3" t="s">
         <v>99</v>
@@ -5723,7 +5733,7 @@
         <v>97</v>
       </c>
       <c r="E4" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F4" t="s">
         <v>100</v>
@@ -5746,7 +5756,7 @@
         <v>97</v>
       </c>
       <c r="E5" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F5" t="s">
         <v>101</v>
@@ -5769,7 +5779,7 @@
         <v>97</v>
       </c>
       <c r="E6" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F6" t="s">
         <v>102</v>
@@ -5792,7 +5802,7 @@
         <v>97</v>
       </c>
       <c r="E7" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F7" t="s">
         <v>103</v>
@@ -5815,7 +5825,7 @@
         <v>97</v>
       </c>
       <c r="E8" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F8" t="s">
         <v>104</v>
@@ -5838,7 +5848,7 @@
         <v>97</v>
       </c>
       <c r="E9" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F9" t="s">
         <v>105</v>
@@ -5861,7 +5871,7 @@
         <v>97</v>
       </c>
       <c r="E10" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F10" t="s">
         <v>106</v>
@@ -5884,7 +5894,7 @@
         <v>97</v>
       </c>
       <c r="E11" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F11" t="s">
         <v>107</v>
@@ -5907,7 +5917,7 @@
         <v>97</v>
       </c>
       <c r="E12" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F12" t="s">
         <v>108</v>
@@ -5930,7 +5940,7 @@
         <v>97</v>
       </c>
       <c r="E13" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F13" t="s">
         <v>109</v>
@@ -5953,7 +5963,7 @@
         <v>97</v>
       </c>
       <c r="E14" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F14" t="s">
         <v>110</v>
@@ -5976,13 +5986,13 @@
         <v>97</v>
       </c>
       <c r="E15" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F15" t="s">
-        <v>263</v>
+        <v>193</v>
       </c>
       <c r="G15" t="s">
-        <v>265</v>
+        <v>195</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -5999,13 +6009,13 @@
         <v>97</v>
       </c>
       <c r="E16" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F16" t="s">
-        <v>264</v>
+        <v>194</v>
       </c>
       <c r="G16" t="s">
-        <v>265</v>
+        <v>195</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
@@ -6022,13 +6032,13 @@
         <v>97</v>
       </c>
       <c r="E17" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F17" t="s">
         <v>113</v>
       </c>
       <c r="G17" t="s">
-        <v>266</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
@@ -6045,7 +6055,7 @@
         <v>114</v>
       </c>
       <c r="E18" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F18" t="s">
         <v>98</v>
@@ -6068,7 +6078,7 @@
         <v>114</v>
       </c>
       <c r="E19" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F19" t="s">
         <v>99</v>
@@ -6091,7 +6101,7 @@
         <v>114</v>
       </c>
       <c r="E20" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F20" t="s">
         <v>100</v>
@@ -6114,7 +6124,7 @@
         <v>114</v>
       </c>
       <c r="E21" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F21" t="s">
         <v>101</v>
@@ -6137,7 +6147,7 @@
         <v>114</v>
       </c>
       <c r="E22" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F22" t="s">
         <v>102</v>
@@ -6160,7 +6170,7 @@
         <v>114</v>
       </c>
       <c r="E23" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F23" t="s">
         <v>103</v>
@@ -6183,7 +6193,7 @@
         <v>114</v>
       </c>
       <c r="E24" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F24" t="s">
         <v>104</v>
@@ -6206,7 +6216,7 @@
         <v>114</v>
       </c>
       <c r="E25" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F25" t="s">
         <v>105</v>
@@ -6229,7 +6239,7 @@
         <v>114</v>
       </c>
       <c r="E26" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F26" t="s">
         <v>106</v>
@@ -6252,7 +6262,7 @@
         <v>114</v>
       </c>
       <c r="E27" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F27" t="s">
         <v>107</v>
@@ -6275,13 +6285,13 @@
         <v>114</v>
       </c>
       <c r="E28" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F28" t="s">
-        <v>208</v>
+        <v>143</v>
       </c>
       <c r="G28" t="s">
-        <v>208</v>
+        <v>143</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
@@ -6298,13 +6308,13 @@
         <v>114</v>
       </c>
       <c r="E29" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F29" t="s">
-        <v>209</v>
+        <v>144</v>
       </c>
       <c r="G29" t="s">
-        <v>209</v>
+        <v>144</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
@@ -6321,13 +6331,13 @@
         <v>114</v>
       </c>
       <c r="E30" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F30" t="s">
         <v>113</v>
       </c>
       <c r="G30" t="s">
-        <v>252</v>
+        <v>182</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
@@ -6344,7 +6354,7 @@
         <v>114</v>
       </c>
       <c r="E31" t="s">
-        <v>234</v>
+        <v>164</v>
       </c>
       <c r="G31" t="s">
         <v>129</v>
@@ -6364,7 +6374,7 @@
         <v>114</v>
       </c>
       <c r="E32" t="s">
-        <v>234</v>
+        <v>164</v>
       </c>
       <c r="G32" t="s">
         <v>129</v>
@@ -6384,7 +6394,7 @@
         <v>114</v>
       </c>
       <c r="E33" t="s">
-        <v>234</v>
+        <v>164</v>
       </c>
       <c r="G33" t="s">
         <v>129</v>
@@ -6404,13 +6414,13 @@
         <v>97</v>
       </c>
       <c r="E34" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F34" t="s">
-        <v>182</v>
+        <v>139</v>
       </c>
       <c r="G34" t="s">
-        <v>235</v>
+        <v>165</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
@@ -6427,13 +6437,13 @@
         <v>97</v>
       </c>
       <c r="E35" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F35" t="s">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="G35" t="s">
-        <v>236</v>
+        <v>166</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
@@ -6450,13 +6460,13 @@
         <v>97</v>
       </c>
       <c r="E36" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F36" t="s">
-        <v>237</v>
+        <v>167</v>
       </c>
       <c r="G36" t="s">
-        <v>230</v>
+        <v>160</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
@@ -6473,13 +6483,13 @@
         <v>97</v>
       </c>
       <c r="E37" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F37" t="s">
-        <v>238</v>
+        <v>168</v>
       </c>
       <c r="G37" t="s">
-        <v>231</v>
+        <v>161</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
@@ -6496,13 +6506,13 @@
         <v>97</v>
       </c>
       <c r="E38" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F38" t="s">
-        <v>239</v>
+        <v>169</v>
       </c>
       <c r="G38" t="s">
-        <v>239</v>
+        <v>169</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
@@ -6519,13 +6529,13 @@
         <v>97</v>
       </c>
       <c r="E39" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F39" t="s">
-        <v>200</v>
+        <v>141</v>
       </c>
       <c r="G39" t="s">
-        <v>240</v>
+        <v>170</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
@@ -6542,13 +6552,13 @@
         <v>97</v>
       </c>
       <c r="E40" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F40" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="G40" t="s">
-        <v>242</v>
+        <v>172</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
@@ -6565,13 +6575,13 @@
         <v>97</v>
       </c>
       <c r="E41" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F41" t="s">
-        <v>243</v>
+        <v>173</v>
       </c>
       <c r="G41" t="s">
-        <v>244</v>
+        <v>174</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
@@ -6588,13 +6598,13 @@
         <v>97</v>
       </c>
       <c r="E42" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F42" t="s">
-        <v>245</v>
+        <v>175</v>
       </c>
       <c r="G42" t="s">
-        <v>221</v>
+        <v>151</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
@@ -6611,13 +6621,13 @@
         <v>97</v>
       </c>
       <c r="E43" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F43" t="s">
-        <v>239</v>
+        <v>169</v>
       </c>
       <c r="G43" t="s">
-        <v>239</v>
+        <v>169</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
@@ -6634,13 +6644,13 @@
         <v>97</v>
       </c>
       <c r="E44" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F44" t="s">
-        <v>246</v>
+        <v>176</v>
       </c>
       <c r="G44" t="s">
-        <v>247</v>
+        <v>177</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
@@ -6657,13 +6667,13 @@
         <v>97</v>
       </c>
       <c r="E45" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F45" t="s">
-        <v>248</v>
+        <v>178</v>
       </c>
       <c r="G45" t="s">
-        <v>249</v>
+        <v>179</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
@@ -6680,13 +6690,13 @@
         <v>97</v>
       </c>
       <c r="E46" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F46" t="s">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="G46" t="s">
-        <v>251</v>
+        <v>181</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
@@ -6703,13 +6713,13 @@
         <v>97</v>
       </c>
       <c r="E47" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F47" t="s">
-        <v>172</v>
+        <v>138</v>
       </c>
       <c r="G47" t="s">
-        <v>219</v>
+        <v>149</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
@@ -6726,13 +6736,13 @@
         <v>97</v>
       </c>
       <c r="E48" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F48" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="G48" t="s">
-        <v>220</v>
+        <v>150</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
@@ -6749,13 +6759,13 @@
         <v>97</v>
       </c>
       <c r="E49" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F49" t="s">
         <v>115</v>
       </c>
       <c r="G49" t="s">
-        <v>222</v>
+        <v>152</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
@@ -6772,7 +6782,7 @@
         <v>114</v>
       </c>
       <c r="E50" t="s">
-        <v>234</v>
+        <v>164</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
@@ -6789,7 +6799,7 @@
         <v>114</v>
       </c>
       <c r="E51" t="s">
-        <v>234</v>
+        <v>164</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
@@ -6806,13 +6816,13 @@
         <v>97</v>
       </c>
       <c r="E52" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F52" t="s">
-        <v>228</v>
+        <v>158</v>
       </c>
       <c r="G52" t="s">
-        <v>228</v>
+        <v>158</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
@@ -6829,13 +6839,13 @@
         <v>97</v>
       </c>
       <c r="E53" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F53" t="s">
-        <v>229</v>
+        <v>159</v>
       </c>
       <c r="G53" t="s">
-        <v>229</v>
+        <v>159</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
@@ -6852,13 +6862,13 @@
         <v>114</v>
       </c>
       <c r="E54" t="s">
-        <v>234</v>
+        <v>164</v>
       </c>
       <c r="F54" t="s">
-        <v>228</v>
+        <v>158</v>
       </c>
       <c r="G54" t="s">
-        <v>228</v>
+        <v>158</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
@@ -6875,13 +6885,13 @@
         <v>114</v>
       </c>
       <c r="E55" t="s">
-        <v>234</v>
+        <v>164</v>
       </c>
       <c r="F55" t="s">
-        <v>229</v>
+        <v>159</v>
       </c>
       <c r="G55" t="s">
-        <v>229</v>
+        <v>159</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
@@ -6898,13 +6908,13 @@
         <v>97</v>
       </c>
       <c r="E56" t="s">
-        <v>234</v>
+        <v>164</v>
       </c>
       <c r="F56" t="s">
-        <v>228</v>
+        <v>158</v>
       </c>
       <c r="G56" t="s">
-        <v>228</v>
+        <v>158</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
@@ -6921,13 +6931,13 @@
         <v>97</v>
       </c>
       <c r="E57" t="s">
-        <v>234</v>
+        <v>164</v>
       </c>
       <c r="F57" t="s">
-        <v>229</v>
+        <v>159</v>
       </c>
       <c r="G57" t="s">
-        <v>229</v>
+        <v>159</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
@@ -6944,7 +6954,7 @@
         <v>114</v>
       </c>
       <c r="E58" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F58" t="s">
         <v>108</v>
@@ -6964,7 +6974,7 @@
         <v>114</v>
       </c>
       <c r="E59" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F59" t="s">
         <v>109</v>
@@ -6984,7 +6994,7 @@
         <v>114</v>
       </c>
       <c r="E60" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F60" t="s">
         <v>110</v>
@@ -7004,7 +7014,7 @@
         <v>114</v>
       </c>
       <c r="E61" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F61" t="s">
         <v>111</v>
@@ -7024,7 +7034,7 @@
         <v>114</v>
       </c>
       <c r="E62" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F62" t="s">
         <v>112</v>
@@ -7044,7 +7054,7 @@
         <v>114</v>
       </c>
       <c r="E63" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F63" t="s">
         <v>113</v>
@@ -7064,7 +7074,7 @@
         <v>114</v>
       </c>
       <c r="E64" t="s">
-        <v>234</v>
+        <v>164</v>
       </c>
       <c r="G64" t="s">
         <v>120</v>
@@ -7083,8 +7093,8 @@
       <c r="D65" t="s">
         <v>114</v>
       </c>
-      <c r="E65" s="10" t="s">
-        <v>234</v>
+      <c r="E65" s="5" t="s">
+        <v>164</v>
       </c>
       <c r="G65" t="s">
         <v>120</v>
@@ -7103,8 +7113,8 @@
       <c r="D66" t="s">
         <v>114</v>
       </c>
-      <c r="E66" s="10" t="s">
-        <v>234</v>
+      <c r="E66" s="5" t="s">
+        <v>164</v>
       </c>
       <c r="G66" t="s">
         <v>120</v>
@@ -7123,8 +7133,8 @@
       <c r="D67" t="s">
         <v>114</v>
       </c>
-      <c r="E67" s="10" t="s">
-        <v>234</v>
+      <c r="E67" s="5" t="s">
+        <v>164</v>
       </c>
       <c r="G67" t="s">
         <v>120</v>
@@ -7143,8 +7153,8 @@
       <c r="D68" t="s">
         <v>114</v>
       </c>
-      <c r="E68" s="10" t="s">
-        <v>234</v>
+      <c r="E68" s="5" t="s">
+        <v>164</v>
       </c>
       <c r="G68" t="s">
         <v>120</v>
@@ -7163,8 +7173,8 @@
       <c r="D69" t="s">
         <v>114</v>
       </c>
-      <c r="E69" s="10" t="s">
-        <v>234</v>
+      <c r="E69" s="5" t="s">
+        <v>164</v>
       </c>
       <c r="G69" t="s">
         <v>120</v>
@@ -7183,8 +7193,8 @@
       <c r="D70" t="s">
         <v>114</v>
       </c>
-      <c r="E70" s="10" t="s">
-        <v>234</v>
+      <c r="E70" s="5" t="s">
+        <v>164</v>
       </c>
       <c r="G70" t="s">
         <v>120</v>
@@ -7203,8 +7213,8 @@
       <c r="D71" t="s">
         <v>114</v>
       </c>
-      <c r="E71" s="10" t="s">
-        <v>234</v>
+      <c r="E71" s="5" t="s">
+        <v>164</v>
       </c>
       <c r="G71" t="s">
         <v>120</v>
@@ -7223,8 +7233,8 @@
       <c r="D72" t="s">
         <v>114</v>
       </c>
-      <c r="E72" s="10" t="s">
-        <v>234</v>
+      <c r="E72" s="5" t="s">
+        <v>164</v>
       </c>
       <c r="G72" t="s">
         <v>120</v>
@@ -7243,8 +7253,8 @@
       <c r="D73" t="s">
         <v>114</v>
       </c>
-      <c r="E73" s="10" t="s">
-        <v>234</v>
+      <c r="E73" s="5" t="s">
+        <v>164</v>
       </c>
       <c r="G73" t="s">
         <v>120</v>
@@ -7263,8 +7273,8 @@
       <c r="D74" t="s">
         <v>97</v>
       </c>
-      <c r="E74" s="10" t="s">
-        <v>234</v>
+      <c r="E74" s="5" t="s">
+        <v>164</v>
       </c>
       <c r="G74" t="s">
         <v>120</v>
@@ -7283,8 +7293,8 @@
       <c r="D75" t="s">
         <v>97</v>
       </c>
-      <c r="E75" s="10" t="s">
-        <v>234</v>
+      <c r="E75" s="5" t="s">
+        <v>164</v>
       </c>
       <c r="G75" t="s">
         <v>120</v>
@@ -7303,8 +7313,8 @@
       <c r="D76" t="s">
         <v>97</v>
       </c>
-      <c r="E76" s="10" t="s">
-        <v>234</v>
+      <c r="E76" s="5" t="s">
+        <v>164</v>
       </c>
       <c r="G76" t="s">
         <v>120</v>
@@ -7323,8 +7333,8 @@
       <c r="D77" t="s">
         <v>97</v>
       </c>
-      <c r="E77" s="10" t="s">
-        <v>234</v>
+      <c r="E77" s="5" t="s">
+        <v>164</v>
       </c>
       <c r="G77" t="s">
         <v>120</v>
@@ -7343,8 +7353,8 @@
       <c r="D78" t="s">
         <v>97</v>
       </c>
-      <c r="E78" s="10" t="s">
-        <v>234</v>
+      <c r="E78" s="5" t="s">
+        <v>164</v>
       </c>
       <c r="G78" t="s">
         <v>120</v>
@@ -7363,8 +7373,8 @@
       <c r="D79" t="s">
         <v>97</v>
       </c>
-      <c r="E79" s="10" t="s">
-        <v>234</v>
+      <c r="E79" s="5" t="s">
+        <v>164</v>
       </c>
       <c r="G79" t="s">
         <v>120</v>
@@ -7383,8 +7393,8 @@
       <c r="D80" t="s">
         <v>97</v>
       </c>
-      <c r="E80" s="10" t="s">
-        <v>234</v>
+      <c r="E80" s="5" t="s">
+        <v>164</v>
       </c>
       <c r="G80" t="s">
         <v>120</v>
@@ -7403,8 +7413,8 @@
       <c r="D81" t="s">
         <v>97</v>
       </c>
-      <c r="E81" s="10" t="s">
-        <v>234</v>
+      <c r="E81" s="5" t="s">
+        <v>164</v>
       </c>
       <c r="G81" t="s">
         <v>120</v>
@@ -7423,8 +7433,8 @@
       <c r="D82" t="s">
         <v>97</v>
       </c>
-      <c r="E82" s="10" t="s">
-        <v>234</v>
+      <c r="E82" s="5" t="s">
+        <v>164</v>
       </c>
       <c r="G82" t="s">
         <v>120</v>
@@ -7443,8 +7453,8 @@
       <c r="D83" t="s">
         <v>97</v>
       </c>
-      <c r="E83" s="10" t="s">
-        <v>234</v>
+      <c r="E83" s="5" t="s">
+        <v>164</v>
       </c>
       <c r="G83" t="s">
         <v>120</v>
@@ -7463,8 +7473,8 @@
       <c r="D84" t="s">
         <v>97</v>
       </c>
-      <c r="E84" s="10" t="s">
-        <v>234</v>
+      <c r="E84" s="5" t="s">
+        <v>164</v>
       </c>
       <c r="G84" t="s">
         <v>120</v>
@@ -7483,8 +7493,8 @@
       <c r="D85" t="s">
         <v>97</v>
       </c>
-      <c r="E85" s="10" t="s">
-        <v>234</v>
+      <c r="E85" s="5" t="s">
+        <v>164</v>
       </c>
       <c r="G85" t="s">
         <v>120</v>
@@ -7503,8 +7513,8 @@
       <c r="D86" t="s">
         <v>97</v>
       </c>
-      <c r="E86" s="10" t="s">
-        <v>234</v>
+      <c r="E86" s="5" t="s">
+        <v>164</v>
       </c>
       <c r="G86" t="s">
         <v>120</v>
@@ -7523,8 +7533,8 @@
       <c r="D87" t="s">
         <v>97</v>
       </c>
-      <c r="E87" s="10" t="s">
-        <v>234</v>
+      <c r="E87" s="5" t="s">
+        <v>164</v>
       </c>
       <c r="G87" t="s">
         <v>120</v>
@@ -7543,8 +7553,8 @@
       <c r="D88" t="s">
         <v>97</v>
       </c>
-      <c r="E88" s="10" t="s">
-        <v>234</v>
+      <c r="E88" s="5" t="s">
+        <v>164</v>
       </c>
       <c r="G88" t="s">
         <v>120</v>
@@ -7563,16 +7573,16 @@
       <c r="D89" t="s">
         <v>97</v>
       </c>
-      <c r="E89" s="10" t="s">
-        <v>234</v>
+      <c r="E89" s="5" t="s">
+        <v>164</v>
       </c>
       <c r="G89" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A90" s="11" t="s">
-        <v>262</v>
+      <c r="A90" s="6" t="s">
+        <v>192</v>
       </c>
       <c r="B90" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -7585,18 +7595,18 @@
         <v>114</v>
       </c>
       <c r="E90" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F90" t="s">
-        <v>257</v>
+        <v>187</v>
       </c>
       <c r="G90" t="s">
-        <v>253</v>
+        <v>183</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A91" s="11" t="s">
-        <v>262</v>
+      <c r="A91" s="6" t="s">
+        <v>192</v>
       </c>
       <c r="B91" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -7609,18 +7619,18 @@
         <v>114</v>
       </c>
       <c r="E91" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F91" t="s">
-        <v>258</v>
+        <v>188</v>
       </c>
       <c r="G91" t="s">
-        <v>254</v>
+        <v>184</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>261</v>
+        <v>191</v>
       </c>
       <c r="B92" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -7633,18 +7643,18 @@
         <v>114</v>
       </c>
       <c r="E92" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F92" t="s">
-        <v>259</v>
-      </c>
-      <c r="G92" s="7" t="s">
-        <v>255</v>
+        <v>189</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>261</v>
+        <v>191</v>
       </c>
       <c r="B93" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -7657,18 +7667,18 @@
         <v>114</v>
       </c>
       <c r="E93" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F93" t="s">
-        <v>260</v>
-      </c>
-      <c r="G93" s="8" t="s">
-        <v>256</v>
+        <v>190</v>
+      </c>
+      <c r="G93" s="4" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B94" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -7681,18 +7691,18 @@
         <v>97</v>
       </c>
       <c r="E94" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F94" t="s">
-        <v>224</v>
+        <v>154</v>
       </c>
       <c r="G94" t="s">
-        <v>267</v>
+        <v>197</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B95" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -7705,18 +7715,18 @@
         <v>97</v>
       </c>
       <c r="E95" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F95" t="s">
-        <v>268</v>
+        <v>198</v>
       </c>
       <c r="G95" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B96" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -7729,18 +7739,18 @@
         <v>97</v>
       </c>
       <c r="E96" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F96" t="s">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="G96" t="s">
-        <v>271</v>
+        <v>201</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B97" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -7753,18 +7763,18 @@
         <v>97</v>
       </c>
       <c r="E97" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="F97" t="s">
-        <v>272</v>
+        <v>202</v>
       </c>
       <c r="G97" t="s">
-        <v>273</v>
+        <v>203</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B98" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -7777,12 +7787,12 @@
         <v>114</v>
       </c>
       <c r="E98" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B99" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -7795,12 +7805,12 @@
         <v>114</v>
       </c>
       <c r="E99" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B100" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -7813,12 +7823,12 @@
         <v>114</v>
       </c>
       <c r="E100" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B101" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -7831,12 +7841,12 @@
         <v>114</v>
       </c>
       <c r="E101" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B102" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -7849,12 +7859,12 @@
         <v>114</v>
       </c>
       <c r="E102" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B103" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -7867,12 +7877,12 @@
         <v>114</v>
       </c>
       <c r="E103" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B104" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -7885,12 +7895,12 @@
         <v>114</v>
       </c>
       <c r="E104" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B105" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -7903,12 +7913,12 @@
         <v>114</v>
       </c>
       <c r="E105" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B106" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -7921,12 +7931,12 @@
         <v>114</v>
       </c>
       <c r="E106" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B107" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -7939,12 +7949,12 @@
         <v>114</v>
       </c>
       <c r="E107" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B108" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -7957,12 +7967,12 @@
         <v>114</v>
       </c>
       <c r="E108" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B109" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -7975,12 +7985,12 @@
         <v>114</v>
       </c>
       <c r="E109" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B110" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -7993,12 +8003,12 @@
         <v>114</v>
       </c>
       <c r="E110" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B111" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -8011,12 +8021,12 @@
         <v>114</v>
       </c>
       <c r="E111" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B112" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -8029,12 +8039,12 @@
         <v>114</v>
       </c>
       <c r="E112" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B113" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -8047,12 +8057,12 @@
         <v>114</v>
       </c>
       <c r="E113" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B114" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -8065,12 +8075,12 @@
         <v>114</v>
       </c>
       <c r="E114" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B115" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -8083,12 +8093,12 @@
         <v>114</v>
       </c>
       <c r="E115" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B116" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -8101,12 +8111,12 @@
         <v>114</v>
       </c>
       <c r="E116" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B117" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -8119,12 +8129,12 @@
         <v>114</v>
       </c>
       <c r="E117" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B118" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -8137,12 +8147,12 @@
         <v>114</v>
       </c>
       <c r="E118" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B119" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -8155,12 +8165,12 @@
         <v>114</v>
       </c>
       <c r="E119" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B120" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -8173,12 +8183,12 @@
         <v>114</v>
       </c>
       <c r="E120" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B121" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -8191,12 +8201,12 @@
         <v>114</v>
       </c>
       <c r="E121" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B122" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -8209,12 +8219,12 @@
         <v>114</v>
       </c>
       <c r="E122" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B123" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -8227,12 +8237,12 @@
         <v>114</v>
       </c>
       <c r="E123" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B124" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -8245,12 +8255,12 @@
         <v>114</v>
       </c>
       <c r="E124" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B125" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -8263,12 +8273,12 @@
         <v>114</v>
       </c>
       <c r="E125" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B126" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -8281,12 +8291,12 @@
         <v>114</v>
       </c>
       <c r="E126" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B127" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -8299,12 +8309,12 @@
         <v>114</v>
       </c>
       <c r="E127" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B128" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -8317,12 +8327,12 @@
         <v>114</v>
       </c>
       <c r="E128" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B129" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -8335,12 +8345,12 @@
         <v>114</v>
       </c>
       <c r="E129" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B130" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -8353,12 +8363,12 @@
         <v>114</v>
       </c>
       <c r="E130" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B131" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -8371,12 +8381,12 @@
         <v>114</v>
       </c>
       <c r="E131" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B132" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -8389,12 +8399,12 @@
         <v>114</v>
       </c>
       <c r="E132" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B133" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -8407,12 +8417,12 @@
         <v>114</v>
       </c>
       <c r="E133" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B134" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -8425,12 +8435,12 @@
         <v>114</v>
       </c>
       <c r="E134" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B135" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -8443,12 +8453,12 @@
         <v>114</v>
       </c>
       <c r="E135" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B136" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -8461,12 +8471,12 @@
         <v>114</v>
       </c>
       <c r="E136" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B137" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -8479,12 +8489,12 @@
         <v>114</v>
       </c>
       <c r="E137" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B138" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -8497,12 +8507,12 @@
         <v>114</v>
       </c>
       <c r="E138" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B139" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -8515,12 +8525,12 @@
         <v>114</v>
       </c>
       <c r="E139" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B140" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -8533,12 +8543,12 @@
         <v>114</v>
       </c>
       <c r="E140" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B141" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -8551,12 +8561,12 @@
         <v>114</v>
       </c>
       <c r="E141" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B142" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -8569,12 +8579,12 @@
         <v>114</v>
       </c>
       <c r="E142" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B143" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -8587,12 +8597,12 @@
         <v>114</v>
       </c>
       <c r="E143" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B144" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -8605,12 +8615,12 @@
         <v>114</v>
       </c>
       <c r="E144" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="B145" s="1" t="str">
         <f>Table4[[#This Row],[Device]]</f>
@@ -8623,7 +8633,7 @@
         <v>114</v>
       </c>
       <c r="E145" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -9097,381 +9107,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B24D4A93-D0E2-2949-A61E-1679DC88B601}">
-  <dimension ref="A1:Y17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="3" max="3" width="14.5" style="6" customWidth="1"/>
-    <col min="5" max="5" width="15.1640625" style="6" customWidth="1"/>
-    <col min="6" max="6" width="24.5" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C2" s="5">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="E2" s="6">
-        <v>1</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>194</v>
-      </c>
-      <c r="C3" s="5">
-        <v>2</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="E3" s="6">
-        <v>2</v>
-      </c>
-      <c r="F3" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>194</v>
-      </c>
-      <c r="C4" s="5">
-        <v>3</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="F4" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>194</v>
-      </c>
-      <c r="C5" s="5">
-        <v>4</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="F5" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>194</v>
-      </c>
-      <c r="C6" s="5">
-        <v>5</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="F6" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>194</v>
-      </c>
-      <c r="C7" s="5">
-        <v>6</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="E7" s="6">
-        <v>13</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" t="s">
-        <v>194</v>
-      </c>
-      <c r="C8" s="5">
-        <v>7</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="E8" s="6">
-        <v>15</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" t="s">
-        <v>194</v>
-      </c>
-      <c r="C9" s="5">
-        <v>8</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="E9" s="6">
-        <v>17</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" t="s">
-        <v>194</v>
-      </c>
-      <c r="C10" s="5">
-        <v>9</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="F10" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" t="s">
-        <v>194</v>
-      </c>
-      <c r="C11" s="5">
-        <v>10</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" t="s">
-        <v>194</v>
-      </c>
-      <c r="C12" s="5">
-        <v>11</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="E12" s="6">
-        <v>11</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" t="s">
-        <v>194</v>
-      </c>
-      <c r="C13" s="5">
-        <v>12</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="E13" s="6">
-        <v>12</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" t="s">
-        <v>194</v>
-      </c>
-      <c r="C14" s="5">
-        <v>13</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="E14" s="6">
-        <v>13</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" t="s">
-        <v>194</v>
-      </c>
-      <c r="C15" s="5">
-        <v>14</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="F15" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" t="s">
-        <v>194</v>
-      </c>
-      <c r="C16" s="5">
-        <v>15</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" t="s">
-        <v>194</v>
-      </c>
-      <c r="C17" s="5">
-        <v>16</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>192</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
 </file>